--- a/research/traditional_assets/database/data/czech_republic/czech_republic_diversified.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08315957847594085</v>
+        <v>0.08303802527683658</v>
       </c>
       <c r="C2">
-        <v>105.6684157254851</v>
+        <v>104.8296134527665</v>
       </c>
       <c r="D2">
-        <v>96.31841572548507</v>
+        <v>96.54161345276647</v>
       </c>
       <c r="E2">
-        <v>-24.1</v>
+        <v>-23.038</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="G2">
         <v>9.35</v>
@@ -1451,28 +1451,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05341859999999999</v>
       </c>
       <c r="N2">
-        <v>7.24734693877551</v>
+        <v>7.19392833877551</v>
       </c>
       <c r="O2">
-        <v>1.376995918367347</v>
+        <v>1.366846384367347</v>
       </c>
       <c r="P2">
-        <v>5.870351020408163</v>
+        <v>5.827081954408163</v>
       </c>
       <c r="Q2">
-        <v>11.99035102040816</v>
+        <v>11.94708195440816</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08315957847594085</v>
+        <v>0.08346524775438038</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7341657850216519</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>135.6708513284794</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08303802527683658</v>
+        <v>0.08291647207773228</v>
       </c>
       <c r="C3">
-        <v>104.8296134527665</v>
+        <v>103.9918480105271</v>
       </c>
       <c r="D3">
-        <v>96.54161345276647</v>
+        <v>96.76584801052715</v>
       </c>
       <c r="E3">
-        <v>-23.038</v>
+        <v>-21.976</v>
       </c>
       <c r="F3">
-        <v>1.062</v>
+        <v>2.124</v>
       </c>
       <c r="G3">
         <v>9.35</v>
@@ -1533,28 +1533,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M3">
-        <v>0.05341859999999999</v>
+        <v>0.1068372</v>
       </c>
       <c r="N3">
-        <v>7.19392833877551</v>
+        <v>7.14050973877551</v>
       </c>
       <c r="O3">
-        <v>1.366846384367347</v>
+        <v>1.356696850367347</v>
       </c>
       <c r="P3">
-        <v>5.827081954408163</v>
+        <v>5.783812888408163</v>
       </c>
       <c r="Q3">
-        <v>11.94708195440816</v>
+        <v>11.90381288840816</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08346524775438038</v>
+        <v>0.08377715518135948</v>
       </c>
       <c r="T3">
-        <v>0.7341657850216519</v>
+        <v>0.740245441326463</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.6708513284794</v>
+        <v>67.83542566423972</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08291647207773228</v>
+        <v>0.082794918878628</v>
       </c>
       <c r="C4">
-        <v>103.9918480105271</v>
+        <v>103.1551266402397</v>
       </c>
       <c r="D4">
-        <v>96.76584801052715</v>
+        <v>96.99112664023973</v>
       </c>
       <c r="E4">
-        <v>-21.976</v>
+        <v>-20.914</v>
       </c>
       <c r="F4">
-        <v>2.124</v>
+        <v>3.185999999999999</v>
       </c>
       <c r="G4">
         <v>9.35</v>
@@ -1615,28 +1615,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M4">
-        <v>0.1068372</v>
+        <v>0.1602558</v>
       </c>
       <c r="N4">
-        <v>7.14050973877551</v>
+        <v>7.08709113877551</v>
       </c>
       <c r="O4">
-        <v>1.356696850367347</v>
+        <v>1.346547316367347</v>
       </c>
       <c r="P4">
-        <v>5.783812888408163</v>
+        <v>5.740543822408164</v>
       </c>
       <c r="Q4">
-        <v>11.90381288840816</v>
+        <v>11.86054382240816</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08377715518135948</v>
+        <v>0.08409549368930722</v>
       </c>
       <c r="T4">
-        <v>0.740245441326463</v>
+        <v>0.7464504513695177</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.83542566423972</v>
+        <v>45.22361710949314</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.082794918878628</v>
+        <v>0.0826733656795237</v>
       </c>
       <c r="C5">
-        <v>103.1551266402397</v>
+        <v>102.3194566509692</v>
       </c>
       <c r="D5">
-        <v>96.99112664023973</v>
+        <v>97.21745665096925</v>
       </c>
       <c r="E5">
-        <v>-20.914</v>
+        <v>-19.852</v>
       </c>
       <c r="F5">
-        <v>3.185999999999999</v>
+        <v>4.247999999999999</v>
       </c>
       <c r="G5">
         <v>9.35</v>
@@ -1697,28 +1697,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M5">
-        <v>0.1602558</v>
+        <v>0.2136744</v>
       </c>
       <c r="N5">
-        <v>7.08709113877551</v>
+        <v>7.03367253877551</v>
       </c>
       <c r="O5">
-        <v>1.346547316367347</v>
+        <v>1.336397782367347</v>
       </c>
       <c r="P5">
-        <v>5.740543822408164</v>
+        <v>5.697274756408163</v>
       </c>
       <c r="Q5">
-        <v>11.86054382240816</v>
+        <v>11.81727475640816</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08409549368930722</v>
+        <v>0.08442046424950386</v>
       </c>
       <c r="T5">
-        <v>0.7464504513695177</v>
+        <v>0.7527847324551359</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.22361710949314</v>
+        <v>33.91771283211985</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0826733656795237</v>
+        <v>0.08255181248041943</v>
       </c>
       <c r="C6">
-        <v>102.3194566509692</v>
+        <v>101.4848454201634</v>
       </c>
       <c r="D6">
-        <v>97.21745665096925</v>
+        <v>97.4448454201634</v>
       </c>
       <c r="E6">
-        <v>-19.852</v>
+        <v>-18.79</v>
       </c>
       <c r="F6">
-        <v>4.247999999999999</v>
+        <v>5.31</v>
       </c>
       <c r="G6">
         <v>9.35</v>
@@ -1779,28 +1779,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M6">
-        <v>0.2136744</v>
+        <v>0.267093</v>
       </c>
       <c r="N6">
-        <v>7.03367253877551</v>
+        <v>6.98025393877551</v>
       </c>
       <c r="O6">
-        <v>1.336397782367347</v>
+        <v>1.326248248367347</v>
       </c>
       <c r="P6">
-        <v>5.697274756408163</v>
+        <v>5.654005690408163</v>
       </c>
       <c r="Q6">
-        <v>11.81727475640816</v>
+        <v>11.77400569040816</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08442046424950386</v>
+        <v>0.08475227629517834</v>
       </c>
       <c r="T6">
-        <v>0.7527847324551359</v>
+        <v>0.7592523668267672</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.91771283211985</v>
+        <v>27.13417026569589</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08255181248041943</v>
+        <v>0.08243025928131513</v>
       </c>
       <c r="C7">
-        <v>101.4848454201634</v>
+        <v>100.6513003944544</v>
       </c>
       <c r="D7">
-        <v>97.4448454201634</v>
+        <v>97.67330039445437</v>
       </c>
       <c r="E7">
-        <v>-18.79</v>
+        <v>-17.728</v>
       </c>
       <c r="F7">
-        <v>5.31</v>
+        <v>6.372</v>
       </c>
       <c r="G7">
         <v>9.35</v>
@@ -1861,28 +1861,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M7">
-        <v>0.267093</v>
+        <v>0.3205116</v>
       </c>
       <c r="N7">
-        <v>6.98025393877551</v>
+        <v>6.92683533877551</v>
       </c>
       <c r="O7">
-        <v>1.326248248367347</v>
+        <v>1.316098714367347</v>
       </c>
       <c r="P7">
-        <v>5.654005690408163</v>
+        <v>5.610736624408164</v>
       </c>
       <c r="Q7">
-        <v>11.77400569040816</v>
+        <v>11.73073662440816</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08475227629517834</v>
+        <v>0.08509114817161184</v>
       </c>
       <c r="T7">
-        <v>0.7592523668267672</v>
+        <v>0.7658576104403482</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.13417026569589</v>
+        <v>22.61180855474657</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08243025928131513</v>
+        <v>0.08230870608221086</v>
       </c>
       <c r="C8">
-        <v>100.6513003944544</v>
+        <v>99.81882909047144</v>
       </c>
       <c r="D8">
-        <v>97.67330039445437</v>
+        <v>97.90282909047144</v>
       </c>
       <c r="E8">
-        <v>-17.728</v>
+        <v>-16.666</v>
       </c>
       <c r="F8">
-        <v>6.371999999999999</v>
+        <v>7.433999999999998</v>
       </c>
       <c r="G8">
         <v>9.35</v>
@@ -1943,28 +1943,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M8">
-        <v>0.3205116</v>
+        <v>0.3739301999999999</v>
       </c>
       <c r="N8">
-        <v>6.92683533877551</v>
+        <v>6.87341673877551</v>
       </c>
       <c r="O8">
-        <v>1.316098714367347</v>
+        <v>1.305949180367347</v>
       </c>
       <c r="P8">
-        <v>5.610736624408164</v>
+        <v>5.567467558408163</v>
       </c>
       <c r="Q8">
-        <v>11.73073662440816</v>
+        <v>11.68746755840816</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08509114817161184</v>
+        <v>0.08543730761528048</v>
       </c>
       <c r="T8">
-        <v>0.7658576104403482</v>
+        <v>0.7726049023036836</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.61180855474657</v>
+        <v>19.38155018978278</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08230870608221084</v>
+        <v>0.08218715288310655</v>
       </c>
       <c r="C9">
-        <v>99.81882909047145</v>
+        <v>98.98743909566566</v>
       </c>
       <c r="D9">
-        <v>97.90282909047146</v>
+        <v>98.13343909566566</v>
       </c>
       <c r="E9">
-        <v>-16.666</v>
+        <v>-15.604</v>
       </c>
       <c r="F9">
-        <v>7.434</v>
+        <v>8.495999999999999</v>
       </c>
       <c r="G9">
         <v>9.35</v>
@@ -2025,28 +2025,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M9">
-        <v>0.3739302</v>
+        <v>0.4273487999999999</v>
       </c>
       <c r="N9">
-        <v>6.87341673877551</v>
+        <v>6.81999813877551</v>
       </c>
       <c r="O9">
-        <v>1.305949180367347</v>
+        <v>1.295799646367347</v>
       </c>
       <c r="P9">
-        <v>5.567467558408163</v>
+        <v>5.524198492408163</v>
       </c>
       <c r="Q9">
-        <v>11.68746755840816</v>
+        <v>11.64419849240816</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08543730761528048</v>
+        <v>0.08579099226424625</v>
       </c>
       <c r="T9">
-        <v>0.7726049023036836</v>
+        <v>0.7794988744249176</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.38155018978277</v>
+        <v>16.95885641605993</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08218715288310655</v>
+        <v>0.08206559968400227</v>
       </c>
       <c r="C10">
-        <v>98.98743909566566</v>
+        <v>98.15713806914566</v>
       </c>
       <c r="D10">
-        <v>98.13343909566566</v>
+        <v>98.36513806914566</v>
       </c>
       <c r="E10">
-        <v>-15.604</v>
+        <v>-14.542</v>
       </c>
       <c r="F10">
-        <v>8.495999999999999</v>
+        <v>9.557999999999998</v>
       </c>
       <c r="G10">
         <v>9.35</v>
@@ -2107,28 +2107,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M10">
-        <v>0.4273487999999999</v>
+        <v>0.4807673999999999</v>
       </c>
       <c r="N10">
-        <v>6.81999813877551</v>
+        <v>6.766579538775511</v>
       </c>
       <c r="O10">
-        <v>1.295799646367347</v>
+        <v>1.285650112367347</v>
       </c>
       <c r="P10">
-        <v>5.524198492408163</v>
+        <v>5.480929426408164</v>
       </c>
       <c r="Q10">
-        <v>11.64419849240816</v>
+        <v>11.60092942640816</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08579099226424625</v>
+        <v>0.08615245020220029</v>
       </c>
       <c r="T10">
-        <v>0.7794988744249176</v>
+        <v>0.7865443624169478</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.95885641605993</v>
+        <v>15.07453903649772</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08206559968400227</v>
+        <v>0.08194404648489799</v>
       </c>
       <c r="C11">
-        <v>98.15713806914566</v>
+        <v>97.32793374252589</v>
       </c>
       <c r="D11">
-        <v>98.36513806914566</v>
+        <v>98.5979337425259</v>
       </c>
       <c r="E11">
-        <v>-14.542</v>
+        <v>-13.48</v>
       </c>
       <c r="F11">
-        <v>9.557999999999998</v>
+        <v>10.62</v>
       </c>
       <c r="G11">
         <v>9.35</v>
@@ -2189,28 +2189,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M11">
-        <v>0.4807673999999999</v>
+        <v>0.5341859999999998</v>
       </c>
       <c r="N11">
-        <v>6.766579538775511</v>
+        <v>6.71316093877551</v>
       </c>
       <c r="O11">
-        <v>1.285650112367347</v>
+        <v>1.275500578367347</v>
       </c>
       <c r="P11">
-        <v>5.480929426408164</v>
+        <v>5.437660360408163</v>
       </c>
       <c r="Q11">
-        <v>11.60092942640816</v>
+        <v>11.55766036040816</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08615245020220029</v>
+        <v>0.08652194053877554</v>
       </c>
       <c r="T11">
-        <v>0.7865443624169478</v>
+        <v>0.7937464168088012</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.07453903649772</v>
+        <v>13.56708513284794</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08194404648489799</v>
+        <v>0.08195614328579369</v>
       </c>
       <c r="C12">
-        <v>97.32793374252589</v>
+        <v>96.2427168882089</v>
       </c>
       <c r="D12">
-        <v>98.5979337425259</v>
+        <v>98.57471688820891</v>
       </c>
       <c r="E12">
-        <v>-13.48</v>
+        <v>-12.418</v>
       </c>
       <c r="F12">
-        <v>10.62</v>
+        <v>11.682</v>
       </c>
       <c r="G12">
         <v>9.35</v>
@@ -2271,45 +2271,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M12">
-        <v>0.5341859999999999</v>
+        <v>0.6051275999999999</v>
       </c>
       <c r="N12">
-        <v>6.71316093877551</v>
+        <v>6.64221933877551</v>
       </c>
       <c r="O12">
-        <v>1.275500578367347</v>
+        <v>1.262021674367347</v>
       </c>
       <c r="P12">
-        <v>5.437660360408163</v>
+        <v>5.380197664408163</v>
       </c>
       <c r="Q12">
-        <v>11.55766036040816</v>
+        <v>11.50019766440816</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08652194053877554</v>
+        <v>0.08689973402898167</v>
       </c>
       <c r="T12">
-        <v>0.7937464168088012</v>
+        <v>0.8011103151195723</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.56708513284794</v>
+        <v>11.9765598838584</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08195614328579369</v>
+        <v>0.08184674008668941</v>
       </c>
       <c r="C13">
-        <v>96.2427168882089</v>
+        <v>95.39108816523188</v>
       </c>
       <c r="D13">
-        <v>98.57471688820891</v>
+        <v>98.78508816523188</v>
       </c>
       <c r="E13">
-        <v>-12.418</v>
+        <v>-11.356</v>
       </c>
       <c r="F13">
-        <v>11.682</v>
+        <v>12.744</v>
       </c>
       <c r="G13">
         <v>9.35</v>
@@ -2353,28 +2353,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M13">
-        <v>0.6051275999999999</v>
+        <v>0.6601391999999999</v>
       </c>
       <c r="N13">
-        <v>6.64221933877551</v>
+        <v>6.58720773877551</v>
       </c>
       <c r="O13">
-        <v>1.262021674367347</v>
+        <v>1.251569470367347</v>
       </c>
       <c r="P13">
-        <v>5.380197664408163</v>
+        <v>5.335638268408164</v>
       </c>
       <c r="Q13">
-        <v>11.50019766440816</v>
+        <v>11.45563826840816</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08689973402898167</v>
+        <v>0.08728611373487433</v>
       </c>
       <c r="T13">
-        <v>0.8011103151195723</v>
+        <v>0.8086415747555884</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.9765598838584</v>
+        <v>10.9785132268702</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08184674008668941</v>
+        <v>0.08173733688758511</v>
       </c>
       <c r="C14">
-        <v>95.39108816523188</v>
+        <v>94.54035928200719</v>
       </c>
       <c r="D14">
-        <v>98.78508816523188</v>
+        <v>98.99635928200719</v>
       </c>
       <c r="E14">
-        <v>-11.356</v>
+        <v>-10.294</v>
       </c>
       <c r="F14">
-        <v>12.744</v>
+        <v>13.806</v>
       </c>
       <c r="G14">
         <v>9.35</v>
@@ -2435,28 +2435,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M14">
-        <v>0.6601391999999999</v>
+        <v>0.7151508</v>
       </c>
       <c r="N14">
-        <v>6.58720773877551</v>
+        <v>6.53219613877551</v>
       </c>
       <c r="O14">
-        <v>1.251569470367347</v>
+        <v>1.241117266367347</v>
       </c>
       <c r="P14">
-        <v>5.335638268408164</v>
+        <v>5.291078872408163</v>
       </c>
       <c r="Q14">
-        <v>11.45563826840816</v>
+        <v>11.41107887240816</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08728611373487433</v>
+        <v>0.08768137573285645</v>
       </c>
       <c r="T14">
-        <v>0.8086415747555884</v>
+        <v>0.8163459667970302</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.9785132268702</v>
+        <v>10.13401220941864</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08173733688758511</v>
+        <v>0.08182071368848082</v>
       </c>
       <c r="C15">
-        <v>94.54035928200719</v>
+        <v>93.31726657474492</v>
       </c>
       <c r="D15">
-        <v>98.99635928200719</v>
+        <v>98.83526657474492</v>
       </c>
       <c r="E15">
-        <v>-10.294</v>
+        <v>-9.232000000000001</v>
       </c>
       <c r="F15">
-        <v>13.806</v>
+        <v>14.868</v>
       </c>
       <c r="G15">
         <v>9.35</v>
@@ -2517,45 +2517,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M15">
-        <v>0.7151508</v>
+        <v>0.795438</v>
       </c>
       <c r="N15">
-        <v>6.53219613877551</v>
+        <v>6.45190893877551</v>
       </c>
       <c r="O15">
-        <v>1.241117266367347</v>
+        <v>1.225862698367347</v>
       </c>
       <c r="P15">
-        <v>5.291078872408163</v>
+        <v>5.226046240408163</v>
       </c>
       <c r="Q15">
-        <v>11.41107887240816</v>
+        <v>11.34604624040816</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08768137573285645</v>
+        <v>0.08808582987032654</v>
       </c>
       <c r="T15">
-        <v>0.8163459667970302</v>
+        <v>0.8242295307464125</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.13401220941864</v>
+        <v>9.111139949028724</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08182071368848082</v>
+        <v>0.08172508048937654</v>
       </c>
       <c r="C16">
-        <v>93.31726657474492</v>
+        <v>92.44008420812402</v>
       </c>
       <c r="D16">
-        <v>98.83526657474492</v>
+        <v>99.02008420812403</v>
       </c>
       <c r="E16">
-        <v>-9.232000000000001</v>
+        <v>-8.17</v>
       </c>
       <c r="F16">
-        <v>14.868</v>
+        <v>15.93</v>
       </c>
       <c r="G16">
         <v>9.35</v>
@@ -2599,28 +2599,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M16">
-        <v>0.795438</v>
+        <v>0.8522550000000001</v>
       </c>
       <c r="N16">
-        <v>6.45190893877551</v>
+        <v>6.39509193877551</v>
       </c>
       <c r="O16">
-        <v>1.225862698367347</v>
+        <v>1.215067468367347</v>
       </c>
       <c r="P16">
-        <v>5.226046240408163</v>
+        <v>5.180024470408163</v>
       </c>
       <c r="Q16">
-        <v>11.34604624040816</v>
+        <v>11.30002447040816</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08808582987032654</v>
+        <v>0.08849980057573711</v>
       </c>
       <c r="T16">
-        <v>0.8242295307464125</v>
+        <v>0.8322985903181331</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.111139949028724</v>
+        <v>8.503730619093474</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08172508048937654</v>
+        <v>0.08162944729027224</v>
       </c>
       <c r="C17">
-        <v>92.44008420812403</v>
+        <v>91.56359433825259</v>
       </c>
       <c r="D17">
-        <v>99.02008420812403</v>
+        <v>99.2055943382526</v>
       </c>
       <c r="E17">
-        <v>-8.170000000000003</v>
+        <v>-7.108000000000004</v>
       </c>
       <c r="F17">
-        <v>15.93</v>
+        <v>16.992</v>
       </c>
       <c r="G17">
         <v>9.35</v>
@@ -2681,28 +2681,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M17">
-        <v>0.8522549999999999</v>
+        <v>0.9090719999999999</v>
       </c>
       <c r="N17">
-        <v>6.395091938775511</v>
+        <v>6.33827493877551</v>
       </c>
       <c r="O17">
-        <v>1.215067468367347</v>
+        <v>1.204272238367347</v>
       </c>
       <c r="P17">
-        <v>5.180024470408163</v>
+        <v>5.134002700408163</v>
       </c>
       <c r="Q17">
-        <v>11.30002447040816</v>
+        <v>11.25400270040816</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08849980057573711</v>
+        <v>0.08892362772651459</v>
       </c>
       <c r="T17">
-        <v>0.8322985903181331</v>
+        <v>0.8405597703558471</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.503730619093478</v>
+        <v>7.972247455400134</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08162944729027224</v>
+        <v>0.08164397409116796</v>
       </c>
       <c r="C18">
-        <v>91.56359433825259</v>
+        <v>90.47337036005879</v>
       </c>
       <c r="D18">
-        <v>99.2055943382526</v>
+        <v>99.1773703600588</v>
       </c>
       <c r="E18">
-        <v>-7.108000000000004</v>
+        <v>-6.046000000000003</v>
       </c>
       <c r="F18">
-        <v>16.992</v>
+        <v>18.054</v>
       </c>
       <c r="G18">
         <v>9.35</v>
@@ -2763,45 +2763,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M18">
-        <v>0.9090719999999999</v>
+        <v>0.9803322</v>
       </c>
       <c r="N18">
-        <v>6.33827493877551</v>
+        <v>6.26701473877551</v>
       </c>
       <c r="O18">
-        <v>1.204272238367347</v>
+        <v>1.190732800367347</v>
       </c>
       <c r="P18">
-        <v>5.134002700408163</v>
+        <v>5.076281938408163</v>
       </c>
       <c r="Q18">
-        <v>11.25400270040816</v>
+        <v>11.19628193840816</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08892362772651459</v>
+        <v>0.08935766757972044</v>
       </c>
       <c r="T18">
-        <v>0.8405597703558471</v>
+        <v>0.8490200149727831</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.972247455400134</v>
+        <v>7.392745988324682</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08164397409116796</v>
+        <v>0.08155482089206367</v>
       </c>
       <c r="C19">
-        <v>90.47337036005879</v>
+        <v>89.58483883102154</v>
       </c>
       <c r="D19">
-        <v>99.1773703600588</v>
+        <v>99.35083883102155</v>
       </c>
       <c r="E19">
-        <v>-6.046000000000003</v>
+        <v>-4.984000000000002</v>
       </c>
       <c r="F19">
-        <v>18.054</v>
+        <v>19.116</v>
       </c>
       <c r="G19">
         <v>9.35</v>
@@ -2845,28 +2845,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M19">
-        <v>0.9803322</v>
+        <v>1.0379988</v>
       </c>
       <c r="N19">
-        <v>6.26701473877551</v>
+        <v>6.209348138775511</v>
       </c>
       <c r="O19">
-        <v>1.190732800367347</v>
+        <v>1.179776146367347</v>
       </c>
       <c r="P19">
-        <v>5.076281938408163</v>
+        <v>5.029571992408163</v>
       </c>
       <c r="Q19">
-        <v>11.19628193840816</v>
+        <v>11.14957199240816</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08935766757972044</v>
+        <v>0.08980229377080937</v>
       </c>
       <c r="T19">
-        <v>0.8490200149727831</v>
+        <v>0.8576866070194004</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.392745988324682</v>
+        <v>6.982037877862201</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08155482089206369</v>
+        <v>0.08146566769295939</v>
       </c>
       <c r="C20">
-        <v>89.5848388310215</v>
+        <v>88.69691518328682</v>
       </c>
       <c r="D20">
-        <v>99.35083883102151</v>
+        <v>99.52491518328682</v>
       </c>
       <c r="E20">
-        <v>-4.984000000000005</v>
+        <v>-3.922000000000004</v>
       </c>
       <c r="F20">
-        <v>19.116</v>
+        <v>20.178</v>
       </c>
       <c r="G20">
         <v>9.35</v>
@@ -2927,28 +2927,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M20">
-        <v>1.0379988</v>
+        <v>1.0956654</v>
       </c>
       <c r="N20">
-        <v>6.209348138775511</v>
+        <v>6.15168153877551</v>
       </c>
       <c r="O20">
-        <v>1.179776146367347</v>
+        <v>1.168819492367347</v>
       </c>
       <c r="P20">
-        <v>5.029571992408163</v>
+        <v>4.982862046408163</v>
       </c>
       <c r="Q20">
-        <v>11.14957199240816</v>
+        <v>11.10286204640816</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08980229377080937</v>
+        <v>0.09025789838636961</v>
       </c>
       <c r="T20">
-        <v>0.8576866070194004</v>
+        <v>0.8665671889930947</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.982037877862202</v>
+        <v>6.61456220007998</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08146566769295939</v>
+        <v>0.08137651449385511</v>
       </c>
       <c r="C21">
-        <v>88.69691518328682</v>
+        <v>87.80960261773829</v>
       </c>
       <c r="D21">
-        <v>99.52491518328682</v>
+        <v>99.69960261773829</v>
       </c>
       <c r="E21">
-        <v>-3.922000000000004</v>
+        <v>-2.860000000000003</v>
       </c>
       <c r="F21">
-        <v>20.178</v>
+        <v>21.24</v>
       </c>
       <c r="G21">
         <v>9.35</v>
@@ -3009,28 +3009,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M21">
-        <v>1.0956654</v>
+        <v>1.153332</v>
       </c>
       <c r="N21">
-        <v>6.15168153877551</v>
+        <v>6.09401493877551</v>
       </c>
       <c r="O21">
-        <v>1.168819492367347</v>
+        <v>1.157862838367347</v>
       </c>
       <c r="P21">
-        <v>4.982862046408163</v>
+        <v>4.936152100408163</v>
       </c>
       <c r="Q21">
-        <v>11.10286204640816</v>
+        <v>11.05615210040816</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09025789838636961</v>
+        <v>0.09072489311731888</v>
       </c>
       <c r="T21">
-        <v>0.8665671889930947</v>
+        <v>0.8756697855161316</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.61456220007998</v>
+        <v>6.28383409007598</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08137651449385511</v>
+        <v>0.08145746129475082</v>
       </c>
       <c r="C22">
-        <v>87.80960261773829</v>
+        <v>86.5889692757475</v>
       </c>
       <c r="D22">
-        <v>99.69960261773829</v>
+        <v>99.5409692757475</v>
       </c>
       <c r="E22">
-        <v>-2.860000000000003</v>
+        <v>-1.798000000000002</v>
       </c>
       <c r="F22">
-        <v>21.24</v>
+        <v>22.302</v>
       </c>
       <c r="G22">
         <v>9.35</v>
@@ -3091,45 +3091,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M22">
-        <v>1.153332</v>
+        <v>1.2333006</v>
       </c>
       <c r="N22">
-        <v>6.09401493877551</v>
+        <v>6.01404633877551</v>
       </c>
       <c r="O22">
-        <v>1.157862838367347</v>
+        <v>1.142668804367347</v>
       </c>
       <c r="P22">
-        <v>4.936152100408163</v>
+        <v>4.871377534408163</v>
       </c>
       <c r="Q22">
-        <v>11.05615210040816</v>
+        <v>10.99137753440816</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09072489311731888</v>
+        <v>0.09120371049968458</v>
       </c>
       <c r="T22">
-        <v>0.8756697855161316</v>
+        <v>0.8850028275207641</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.28383409007598</v>
+        <v>5.876383210042637</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08145746129475082</v>
+        <v>0.08137640809564652</v>
       </c>
       <c r="C23">
-        <v>86.5889692757475</v>
+        <v>85.68581146153105</v>
       </c>
       <c r="D23">
-        <v>99.5409692757475</v>
+        <v>99.69981146153106</v>
       </c>
       <c r="E23">
-        <v>-1.798000000000005</v>
+        <v>-0.7360000000000042</v>
       </c>
       <c r="F23">
-        <v>22.302</v>
+        <v>23.364</v>
       </c>
       <c r="G23">
         <v>9.35</v>
@@ -3173,28 +3173,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M23">
-        <v>1.2333006</v>
+        <v>1.2920292</v>
       </c>
       <c r="N23">
-        <v>6.01404633877551</v>
+        <v>5.95531773877551</v>
       </c>
       <c r="O23">
-        <v>1.142668804367347</v>
+        <v>1.131510370367347</v>
       </c>
       <c r="P23">
-        <v>4.871377534408163</v>
+        <v>4.823807368408163</v>
       </c>
       <c r="Q23">
-        <v>10.99137753440816</v>
+        <v>10.94380736840816</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09120371049968458</v>
+        <v>0.09169480525082888</v>
       </c>
       <c r="T23">
-        <v>0.8850028275207641</v>
+        <v>0.8945751782947462</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.876383210042638</v>
+        <v>5.609274882313426</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08137640809564652</v>
+        <v>0.08129535489654224</v>
       </c>
       <c r="C24">
-        <v>85.68581146153105</v>
+        <v>84.78316140138909</v>
       </c>
       <c r="D24">
-        <v>99.69981146153106</v>
+        <v>99.8591614013891</v>
       </c>
       <c r="E24">
-        <v>-0.7360000000000042</v>
+        <v>0.325999999999997</v>
       </c>
       <c r="F24">
-        <v>23.364</v>
+        <v>24.426</v>
       </c>
       <c r="G24">
         <v>9.35</v>
@@ -3255,28 +3255,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M24">
-        <v>1.2920292</v>
+        <v>1.3507578</v>
       </c>
       <c r="N24">
-        <v>5.95531773877551</v>
+        <v>5.89658913877551</v>
       </c>
       <c r="O24">
-        <v>1.131510370367347</v>
+        <v>1.120351936367347</v>
       </c>
       <c r="P24">
-        <v>4.823807368408163</v>
+        <v>4.776237202408163</v>
       </c>
       <c r="Q24">
-        <v>10.94380736840816</v>
+        <v>10.89623720240816</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09169480525082888</v>
+        <v>0.09219865570979512</v>
       </c>
       <c r="T24">
-        <v>0.8945751782947462</v>
+        <v>0.9043961615563643</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.609274882313426</v>
+        <v>5.365393365691103</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08129535489654224</v>
+        <v>0.08121430169743796</v>
       </c>
       <c r="C25">
-        <v>84.78316140138909</v>
+        <v>83.88102153384511</v>
       </c>
       <c r="D25">
-        <v>99.8591614013891</v>
+        <v>100.0190215338451</v>
       </c>
       <c r="E25">
-        <v>0.325999999999997</v>
+        <v>1.387999999999998</v>
       </c>
       <c r="F25">
-        <v>24.426</v>
+        <v>25.488</v>
       </c>
       <c r="G25">
         <v>9.35</v>
@@ -3337,28 +3337,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M25">
-        <v>1.3507578</v>
+        <v>1.4094864</v>
       </c>
       <c r="N25">
-        <v>5.89658913877551</v>
+        <v>5.83786053877551</v>
       </c>
       <c r="O25">
-        <v>1.120351936367347</v>
+        <v>1.109193502367347</v>
       </c>
       <c r="P25">
-        <v>4.776237202408163</v>
+        <v>4.728667036408163</v>
       </c>
       <c r="Q25">
-        <v>10.89623720240816</v>
+        <v>10.84866703640816</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09219865570979512</v>
+        <v>0.09271576539136572</v>
       </c>
       <c r="T25">
-        <v>0.9043961615563643</v>
+        <v>0.9144755917459196</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.365393365691103</v>
+        <v>5.141835308787307</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08121430169743796</v>
+        <v>0.08113324849833368</v>
       </c>
       <c r="C26">
-        <v>83.88102153384511</v>
+        <v>82.9793943130624</v>
       </c>
       <c r="D26">
-        <v>100.0190215338451</v>
+        <v>100.1793943130624</v>
       </c>
       <c r="E26">
-        <v>1.387999999999995</v>
+        <v>2.449999999999996</v>
       </c>
       <c r="F26">
-        <v>25.488</v>
+        <v>26.55</v>
       </c>
       <c r="G26">
         <v>9.35</v>
@@ -3419,28 +3419,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M26">
-        <v>1.4094864</v>
+        <v>1.468215</v>
       </c>
       <c r="N26">
-        <v>5.83786053877551</v>
+        <v>5.77913193877551</v>
       </c>
       <c r="O26">
-        <v>1.109193502367347</v>
+        <v>1.098035068367347</v>
       </c>
       <c r="P26">
-        <v>4.728667036408163</v>
+        <v>4.681096870408163</v>
       </c>
       <c r="Q26">
-        <v>10.84866703640816</v>
+        <v>10.80109687040816</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09271576539136572</v>
+        <v>0.09324666466444489</v>
       </c>
       <c r="T26">
-        <v>0.9144755917459196</v>
+        <v>0.9248238067405298</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.141835308787308</v>
+        <v>4.936161896435816</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08113324849833368</v>
+        <v>0.08105219529922938</v>
       </c>
       <c r="C27">
-        <v>82.9793943130624</v>
+        <v>82.07828220896987</v>
       </c>
       <c r="D27">
-        <v>100.1793943130624</v>
+        <v>100.3402822089699</v>
       </c>
       <c r="E27">
-        <v>2.449999999999996</v>
+        <v>3.511999999999997</v>
       </c>
       <c r="F27">
-        <v>26.55</v>
+        <v>27.612</v>
       </c>
       <c r="G27">
         <v>9.35</v>
@@ -3501,28 +3501,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M27">
-        <v>1.468215</v>
+        <v>1.5269436</v>
       </c>
       <c r="N27">
-        <v>5.77913193877551</v>
+        <v>5.72040333877551</v>
       </c>
       <c r="O27">
-        <v>1.098035068367347</v>
+        <v>1.086876634367347</v>
       </c>
       <c r="P27">
-        <v>4.681096870408163</v>
+        <v>4.633526704408164</v>
       </c>
       <c r="Q27">
-        <v>10.80109687040816</v>
+        <v>10.75352670440816</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09324666466444489</v>
+        <v>0.09379191256652619</v>
       </c>
       <c r="T27">
-        <v>0.9248238067405298</v>
+        <v>0.9354517032214807</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.936161896435816</v>
+        <v>4.746309515803668</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08105219529922938</v>
+        <v>0.08097114210012508</v>
       </c>
       <c r="C28">
-        <v>82.07828220896987</v>
+        <v>81.17768770738866</v>
       </c>
       <c r="D28">
-        <v>100.3402822089699</v>
+        <v>100.5016877073887</v>
       </c>
       <c r="E28">
-        <v>3.511999999999997</v>
+        <v>4.573999999999998</v>
       </c>
       <c r="F28">
-        <v>27.612</v>
+        <v>28.674</v>
       </c>
       <c r="G28">
         <v>9.35</v>
@@ -3583,28 +3583,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M28">
-        <v>1.5269436</v>
+        <v>1.5856722</v>
       </c>
       <c r="N28">
-        <v>5.72040333877551</v>
+        <v>5.66167473877551</v>
       </c>
       <c r="O28">
-        <v>1.086876634367347</v>
+        <v>1.075718200367347</v>
       </c>
       <c r="P28">
-        <v>4.633526704408164</v>
+        <v>4.585956538408163</v>
       </c>
       <c r="Q28">
-        <v>10.75352670440816</v>
+        <v>10.70595653840816</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09379191256652619</v>
+        <v>0.09435209876729464</v>
       </c>
       <c r="T28">
-        <v>0.9354517032214807</v>
+        <v>0.9463707749484851</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.746309515803668</v>
+        <v>4.570520274477606</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08097114210012508</v>
+        <v>0.0814570889010208</v>
       </c>
       <c r="C29">
-        <v>81.17768770738866</v>
+        <v>79.15569790862114</v>
       </c>
       <c r="D29">
-        <v>100.5016877073887</v>
+        <v>99.54169790862115</v>
       </c>
       <c r="E29">
-        <v>4.573999999999998</v>
+        <v>5.635999999999999</v>
       </c>
       <c r="F29">
-        <v>28.674</v>
+        <v>29.736</v>
       </c>
       <c r="G29">
         <v>9.35</v>
@@ -3665,45 +3665,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M29">
-        <v>1.5856722</v>
+        <v>1.7187408</v>
       </c>
       <c r="N29">
-        <v>5.66167473877551</v>
+        <v>5.52860613877551</v>
       </c>
       <c r="O29">
-        <v>1.075718200367347</v>
+        <v>1.050435166367347</v>
       </c>
       <c r="P29">
-        <v>4.585956538408163</v>
+        <v>4.478170972408163</v>
       </c>
       <c r="Q29">
-        <v>10.70595653840816</v>
+        <v>10.59817097240816</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09435209876729464</v>
+        <v>0.09492784569586221</v>
       </c>
       <c r="T29">
-        <v>0.9463707749484851</v>
+        <v>0.9575931542234618</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.19</v>
       </c>
       <c r="W29">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.570520274477606</v>
+        <v>4.216660789559141</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0814570889010208</v>
+        <v>0.08139628570191652</v>
       </c>
       <c r="C30">
-        <v>79.15569790862114</v>
+        <v>78.21280987045279</v>
       </c>
       <c r="D30">
-        <v>99.54169790862115</v>
+        <v>99.66080987045279</v>
       </c>
       <c r="E30">
-        <v>5.635999999999999</v>
+        <v>6.698</v>
       </c>
       <c r="F30">
-        <v>29.736</v>
+        <v>30.798</v>
       </c>
       <c r="G30">
         <v>9.35</v>
@@ -3747,28 +3747,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M30">
-        <v>1.7187408</v>
+        <v>1.7801244</v>
       </c>
       <c r="N30">
-        <v>5.52860613877551</v>
+        <v>5.46722253877551</v>
       </c>
       <c r="O30">
-        <v>1.050435166367347</v>
+        <v>1.038772282367347</v>
       </c>
       <c r="P30">
-        <v>4.478170972408163</v>
+        <v>4.428450256408163</v>
       </c>
       <c r="Q30">
-        <v>10.59817097240816</v>
+        <v>10.54845025640816</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09492784569586221</v>
+        <v>0.09551981084776975</v>
       </c>
       <c r="T30">
-        <v>0.9575931542234618</v>
+        <v>0.9691316568582973</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.216660789559141</v>
+        <v>4.071258693367446</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08139628570191651</v>
+        <v>0.08218598250281223</v>
       </c>
       <c r="C31">
-        <v>78.21280987045282</v>
+        <v>75.62566481490741</v>
       </c>
       <c r="D31">
-        <v>99.66080987045282</v>
+        <v>98.13566481490741</v>
       </c>
       <c r="E31">
-        <v>6.697999999999993</v>
+        <v>7.759999999999994</v>
       </c>
       <c r="F31">
-        <v>30.79799999999999</v>
+        <v>31.86</v>
       </c>
       <c r="G31">
         <v>9.35</v>
@@ -3829,45 +3829,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M31">
-        <v>1.7801244</v>
+        <v>1.953018</v>
       </c>
       <c r="N31">
-        <v>5.46722253877551</v>
+        <v>5.294328938775511</v>
       </c>
       <c r="O31">
-        <v>1.038772282367347</v>
+        <v>1.005922498367347</v>
       </c>
       <c r="P31">
-        <v>4.428450256408163</v>
+        <v>4.288406440408163</v>
       </c>
       <c r="Q31">
-        <v>10.54845025640816</v>
+        <v>10.40840644040816</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09551981084776974</v>
+        <v>0.09612868928973176</v>
       </c>
       <c r="T31">
-        <v>0.9691316568582972</v>
+        <v>0.980999830996985</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.19</v>
       </c>
       <c r="W31">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.071258693367447</v>
+        <v>3.710844927581574</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08218598250281223</v>
+        <v>0.08215352930370794</v>
       </c>
       <c r="C32">
-        <v>75.62566481490741</v>
+        <v>74.62542149748843</v>
       </c>
       <c r="D32">
-        <v>98.13566481490741</v>
+        <v>98.19742149748843</v>
       </c>
       <c r="E32">
-        <v>7.759999999999994</v>
+        <v>8.821999999999996</v>
       </c>
       <c r="F32">
-        <v>31.86</v>
+        <v>32.922</v>
       </c>
       <c r="G32">
         <v>9.35</v>
@@ -3911,28 +3911,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M32">
-        <v>1.953018</v>
+        <v>2.0181186</v>
       </c>
       <c r="N32">
-        <v>5.294328938775511</v>
+        <v>5.22922833877551</v>
       </c>
       <c r="O32">
-        <v>1.005922498367347</v>
+        <v>0.9935533843673469</v>
       </c>
       <c r="P32">
-        <v>4.288406440408163</v>
+        <v>4.235674954408163</v>
       </c>
       <c r="Q32">
-        <v>10.40840644040816</v>
+        <v>10.35567495440816</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09612868928973176</v>
+        <v>0.09675521638218543</v>
       </c>
       <c r="T32">
-        <v>0.980999830996985</v>
+        <v>0.9932120101831708</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.710844927581574</v>
+        <v>3.591140252498298</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08215352930370794</v>
+        <v>0.08284683610460365</v>
       </c>
       <c r="C33">
-        <v>74.62542149748843</v>
+        <v>72.26077849710551</v>
       </c>
       <c r="D33">
-        <v>98.19742149748843</v>
+        <v>96.89477849710551</v>
       </c>
       <c r="E33">
-        <v>8.821999999999996</v>
+        <v>9.883999999999993</v>
       </c>
       <c r="F33">
-        <v>32.922</v>
+        <v>33.98399999999999</v>
       </c>
       <c r="G33">
         <v>9.35</v>
@@ -3993,45 +3993,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M33">
-        <v>2.0181186</v>
+        <v>2.1783744</v>
       </c>
       <c r="N33">
-        <v>5.22922833877551</v>
+        <v>5.06897253877551</v>
       </c>
       <c r="O33">
-        <v>0.9935533843673469</v>
+        <v>0.9631047823673469</v>
       </c>
       <c r="P33">
-        <v>4.235674954408163</v>
+        <v>4.105867756408163</v>
       </c>
       <c r="Q33">
-        <v>10.35567495440816</v>
+        <v>10.22586775640816</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09675521638218543</v>
+        <v>0.0974001707420642</v>
       </c>
       <c r="T33">
-        <v>0.9932120101831708</v>
+        <v>1.005783371110127</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.19</v>
       </c>
       <c r="W33">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.591140252498298</v>
+        <v>3.326951941216125</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08284683610460365</v>
+        <v>0.08283706290549937</v>
       </c>
       <c r="C34">
-        <v>72.26077849710551</v>
+        <v>71.21690100118678</v>
       </c>
       <c r="D34">
-        <v>96.89477849710551</v>
+        <v>96.9129010011868</v>
       </c>
       <c r="E34">
-        <v>9.883999999999993</v>
+        <v>10.946</v>
       </c>
       <c r="F34">
-        <v>33.98399999999999</v>
+        <v>35.046</v>
       </c>
       <c r="G34">
         <v>9.35</v>
@@ -4075,28 +4075,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M34">
-        <v>2.1783744</v>
+        <v>2.2464486</v>
       </c>
       <c r="N34">
-        <v>5.06897253877551</v>
+        <v>5.00089833877551</v>
       </c>
       <c r="O34">
-        <v>0.9631047823673469</v>
+        <v>0.950170684367347</v>
       </c>
       <c r="P34">
-        <v>4.105867756408163</v>
+        <v>4.050727654408163</v>
       </c>
       <c r="Q34">
-        <v>10.22586775640816</v>
+        <v>10.17072765440816</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0974001707420642</v>
+        <v>0.09806437747089458</v>
       </c>
       <c r="T34">
-        <v>1.005783371110127</v>
+        <v>1.018729996542365</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.326951941216125</v>
+        <v>3.226135215724727</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08283706290549937</v>
+        <v>0.08282728970639508</v>
       </c>
       <c r="C35">
-        <v>71.21690100118678</v>
+        <v>70.17303028554247</v>
       </c>
       <c r="D35">
-        <v>96.9129010011868</v>
+        <v>96.93103028554246</v>
       </c>
       <c r="E35">
-        <v>10.946</v>
+        <v>12.008</v>
       </c>
       <c r="F35">
-        <v>35.046</v>
+        <v>36.108</v>
       </c>
       <c r="G35">
         <v>9.35</v>
@@ -4157,28 +4157,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M35">
-        <v>2.2464486</v>
+        <v>2.3145228</v>
       </c>
       <c r="N35">
-        <v>5.00089833877551</v>
+        <v>4.93282413877551</v>
       </c>
       <c r="O35">
-        <v>0.950170684367347</v>
+        <v>0.937236586367347</v>
       </c>
       <c r="P35">
-        <v>4.050727654408163</v>
+        <v>3.995587552408163</v>
       </c>
       <c r="Q35">
-        <v>10.17072765440816</v>
+        <v>10.11558755240816</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09806437747089458</v>
+        <v>0.09874871167635618</v>
       </c>
       <c r="T35">
-        <v>1.018729996542365</v>
+        <v>1.032068943957399</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.226135215724727</v>
+        <v>3.13124888585047</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08282728970639508</v>
+        <v>0.08281751650729079</v>
       </c>
       <c r="C36">
-        <v>70.17303028554247</v>
+        <v>69.12916635397833</v>
       </c>
       <c r="D36">
-        <v>96.93103028554246</v>
+        <v>96.94916635397834</v>
       </c>
       <c r="E36">
-        <v>12.008</v>
+        <v>13.07</v>
       </c>
       <c r="F36">
-        <v>36.108</v>
+        <v>37.17</v>
       </c>
       <c r="G36">
         <v>9.35</v>
@@ -4239,28 +4239,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M36">
-        <v>2.3145228</v>
+        <v>2.382597</v>
       </c>
       <c r="N36">
-        <v>4.93282413877551</v>
+        <v>4.86474993877551</v>
       </c>
       <c r="O36">
-        <v>0.937236586367347</v>
+        <v>0.924302488367347</v>
       </c>
       <c r="P36">
-        <v>3.995587552408163</v>
+        <v>3.940447450408163</v>
       </c>
       <c r="Q36">
-        <v>10.11558755240816</v>
+        <v>10.06044745040816</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09874871167635618</v>
+        <v>0.0994541023189089</v>
       </c>
       <c r="T36">
-        <v>1.032068943957399</v>
+        <v>1.045818320523664</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.13124888585047</v>
+        <v>3.041784631969028</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08281751650729079</v>
+        <v>0.0850822233081865</v>
       </c>
       <c r="C37">
-        <v>69.12916635397833</v>
+        <v>64.03844850961902</v>
       </c>
       <c r="D37">
-        <v>96.94916635397834</v>
+        <v>92.92044850961902</v>
       </c>
       <c r="E37">
-        <v>13.07</v>
+        <v>14.132</v>
       </c>
       <c r="F37">
-        <v>37.17</v>
+        <v>38.232</v>
       </c>
       <c r="G37">
         <v>9.35</v>
@@ -4321,45 +4321,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M37">
-        <v>2.382597</v>
+        <v>2.7488808</v>
       </c>
       <c r="N37">
-        <v>4.86474993877551</v>
+        <v>4.49846613877551</v>
       </c>
       <c r="O37">
-        <v>0.924302488367347</v>
+        <v>0.8547085663673468</v>
       </c>
       <c r="P37">
-        <v>3.940447450408163</v>
+        <v>3.643757572408163</v>
       </c>
       <c r="Q37">
-        <v>10.06044745040816</v>
+        <v>9.763757572408164</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0994541023189089</v>
+        <v>0.1001815364190414</v>
       </c>
       <c r="T37">
-        <v>1.045818320523664</v>
+        <v>1.059997365107625</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.041784631969028</v>
+        <v>2.636471882947966</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0850822233081865</v>
+        <v>0.08513563010908221</v>
       </c>
       <c r="C38">
-        <v>64.03844850961903</v>
+        <v>62.88547954146277</v>
       </c>
       <c r="D38">
-        <v>92.92044850961902</v>
+        <v>92.82947954146277</v>
       </c>
       <c r="E38">
-        <v>14.13199999999999</v>
+        <v>15.194</v>
       </c>
       <c r="F38">
-        <v>38.23199999999999</v>
+        <v>39.294</v>
       </c>
       <c r="G38">
         <v>9.35</v>
@@ -4403,28 +4403,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M38">
-        <v>2.7488808</v>
+        <v>2.8252386</v>
       </c>
       <c r="N38">
-        <v>4.498466138775511</v>
+        <v>4.42210833877551</v>
       </c>
       <c r="O38">
-        <v>0.854708566367347</v>
+        <v>0.840200584367347</v>
       </c>
       <c r="P38">
-        <v>3.643757572408163</v>
+        <v>3.581907754408164</v>
       </c>
       <c r="Q38">
-        <v>9.763757572408164</v>
+        <v>9.701907754408165</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1001815364190414</v>
+        <v>0.1009320636652098</v>
       </c>
       <c r="T38">
-        <v>1.059997365107625</v>
+        <v>1.074626538091077</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.636471882947966</v>
+        <v>2.565215886111534</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08513563010908221</v>
+        <v>0.08638945690997793</v>
       </c>
       <c r="C39">
-        <v>62.88547954146277</v>
+        <v>59.73783597627518</v>
       </c>
       <c r="D39">
-        <v>92.82947954146277</v>
+        <v>90.74383597627518</v>
       </c>
       <c r="E39">
-        <v>15.194</v>
+        <v>16.25599999999999</v>
       </c>
       <c r="F39">
-        <v>39.294</v>
+        <v>40.35599999999999</v>
       </c>
       <c r="G39">
         <v>9.35</v>
@@ -4485,45 +4485,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M39">
-        <v>2.8252386</v>
+        <v>3.0589848</v>
       </c>
       <c r="N39">
-        <v>4.42210833877551</v>
+        <v>4.18836213877551</v>
       </c>
       <c r="O39">
-        <v>0.840200584367347</v>
+        <v>0.7957888063673468</v>
       </c>
       <c r="P39">
-        <v>3.581907754408164</v>
+        <v>3.392573332408163</v>
       </c>
       <c r="Q39">
-        <v>9.701907754408165</v>
+        <v>9.512573332408163</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1009320636652098</v>
+        <v>0.1017068014677063</v>
       </c>
       <c r="T39">
-        <v>1.074626538091077</v>
+        <v>1.089727619880446</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.19</v>
       </c>
       <c r="W39">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.565215886111534</v>
+        <v>2.36920004923709</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08638945690997793</v>
+        <v>0.08647445371087364</v>
       </c>
       <c r="C40">
-        <v>59.73783597627518</v>
+        <v>58.53783715304933</v>
       </c>
       <c r="D40">
-        <v>90.74383597627518</v>
+        <v>90.60583715304934</v>
       </c>
       <c r="E40">
-        <v>16.25599999999999</v>
+        <v>17.318</v>
       </c>
       <c r="F40">
-        <v>40.35599999999999</v>
+        <v>41.418</v>
       </c>
       <c r="G40">
         <v>9.35</v>
@@ -4567,28 +4567,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M40">
-        <v>3.0589848</v>
+        <v>3.1394844</v>
       </c>
       <c r="N40">
-        <v>4.18836213877551</v>
+        <v>4.10786253877551</v>
       </c>
       <c r="O40">
-        <v>0.7957888063673468</v>
+        <v>0.780493882367347</v>
       </c>
       <c r="P40">
-        <v>3.392573332408163</v>
+        <v>3.327368656408163</v>
       </c>
       <c r="Q40">
-        <v>9.512573332408163</v>
+        <v>9.447368656408162</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1017068014677063</v>
+        <v>0.1025069405096289</v>
       </c>
       <c r="T40">
-        <v>1.089727619880446</v>
+        <v>1.105323819105533</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.36920004923709</v>
+        <v>2.308451330025883</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08647445371087364</v>
+        <v>0.08655945051176936</v>
       </c>
       <c r="C41">
-        <v>58.53783715304933</v>
+        <v>57.33825741632749</v>
       </c>
       <c r="D41">
-        <v>90.60583715304934</v>
+        <v>90.46825741632749</v>
       </c>
       <c r="E41">
-        <v>17.318</v>
+        <v>18.38</v>
       </c>
       <c r="F41">
-        <v>41.418</v>
+        <v>42.48</v>
       </c>
       <c r="G41">
         <v>9.35</v>
@@ -4649,28 +4649,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M41">
-        <v>3.1394844</v>
+        <v>3.219984</v>
       </c>
       <c r="N41">
-        <v>4.10786253877551</v>
+        <v>4.02736293877551</v>
       </c>
       <c r="O41">
-        <v>0.780493882367347</v>
+        <v>0.7651989583673469</v>
       </c>
       <c r="P41">
-        <v>3.327368656408163</v>
+        <v>3.262163980408163</v>
       </c>
       <c r="Q41">
-        <v>9.447368656408162</v>
+        <v>9.382163980408162</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1025069405096289</v>
+        <v>0.1033337508529489</v>
       </c>
       <c r="T41">
-        <v>1.105323819105533</v>
+        <v>1.121439891638123</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.308451330025883</v>
+        <v>2.250740046775236</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08655945051176936</v>
+        <v>0.08664444731266507</v>
       </c>
       <c r="C42">
-        <v>57.33825741632749</v>
+        <v>56.13909485992802</v>
       </c>
       <c r="D42">
-        <v>90.46825741632749</v>
+        <v>90.33109485992803</v>
       </c>
       <c r="E42">
-        <v>18.38</v>
+        <v>19.442</v>
       </c>
       <c r="F42">
-        <v>42.48</v>
+        <v>43.542</v>
       </c>
       <c r="G42">
         <v>9.35</v>
@@ -4731,28 +4731,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M42">
-        <v>3.219984</v>
+        <v>3.3004836</v>
       </c>
       <c r="N42">
-        <v>4.02736293877551</v>
+        <v>3.94686333877551</v>
       </c>
       <c r="O42">
-        <v>0.7651989583673469</v>
+        <v>0.7499040343673469</v>
       </c>
       <c r="P42">
-        <v>3.262163980408163</v>
+        <v>3.196959304408163</v>
       </c>
       <c r="Q42">
-        <v>9.382163980408162</v>
+        <v>9.316959304408163</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1033337508529489</v>
+        <v>0.104188588665534</v>
       </c>
       <c r="T42">
-        <v>1.121439891638123</v>
+        <v>1.13810227171419</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.250740046775236</v>
+        <v>2.1958439480734</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08664444731266507</v>
+        <v>0.08672944411356077</v>
       </c>
       <c r="C43">
-        <v>56.13909485992802</v>
+        <v>54.94034758921202</v>
       </c>
       <c r="D43">
-        <v>90.33109485992803</v>
+        <v>90.19434758921203</v>
       </c>
       <c r="E43">
-        <v>19.442</v>
+        <v>20.504</v>
       </c>
       <c r="F43">
-        <v>43.542</v>
+        <v>44.604</v>
       </c>
       <c r="G43">
         <v>9.35</v>
@@ -4813,28 +4813,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M43">
-        <v>3.3004836</v>
+        <v>3.3809832</v>
       </c>
       <c r="N43">
-        <v>3.94686333877551</v>
+        <v>3.86636373877551</v>
       </c>
       <c r="O43">
-        <v>0.7499040343673469</v>
+        <v>0.7346091103673469</v>
       </c>
       <c r="P43">
-        <v>3.196959304408163</v>
+        <v>3.131754628408163</v>
       </c>
       <c r="Q43">
-        <v>9.316959304408163</v>
+        <v>9.251754628408163</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.104188588665534</v>
+        <v>0.1050729036440703</v>
       </c>
       <c r="T43">
-        <v>1.13810227171419</v>
+        <v>1.155339216620466</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.1958439480734</v>
+        <v>2.143561949309748</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08672944411356079</v>
+        <v>0.0868144409144565</v>
       </c>
       <c r="C44">
-        <v>54.940347589212</v>
+        <v>53.74201372099587</v>
       </c>
       <c r="D44">
-        <v>90.194347589212</v>
+        <v>90.05801372099587</v>
       </c>
       <c r="E44">
-        <v>20.50399999999999</v>
+        <v>21.566</v>
       </c>
       <c r="F44">
-        <v>44.60399999999999</v>
+        <v>45.666</v>
       </c>
       <c r="G44">
         <v>9.35</v>
@@ -4895,28 +4895,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M44">
-        <v>3.3809832</v>
+        <v>3.4614828</v>
       </c>
       <c r="N44">
-        <v>3.86636373877551</v>
+        <v>3.78586413877551</v>
       </c>
       <c r="O44">
-        <v>0.734609110367347</v>
+        <v>0.7193141863673469</v>
       </c>
       <c r="P44">
-        <v>3.131754628408163</v>
+        <v>3.066549952408163</v>
       </c>
       <c r="Q44">
-        <v>9.251754628408163</v>
+        <v>9.186549952408164</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1050729036440703</v>
+        <v>0.1059882472183447</v>
       </c>
       <c r="T44">
-        <v>1.155339216620466</v>
+        <v>1.173180966611173</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.143561949309748</v>
+        <v>2.093711671418824</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0868144409144565</v>
+        <v>0.08689943771535222</v>
       </c>
       <c r="C45">
-        <v>53.74201372099587</v>
+        <v>52.54409138346507</v>
       </c>
       <c r="D45">
-        <v>90.05801372099587</v>
+        <v>89.92209138346507</v>
       </c>
       <c r="E45">
-        <v>21.566</v>
+        <v>22.62799999999999</v>
       </c>
       <c r="F45">
-        <v>45.666</v>
+        <v>46.72799999999999</v>
       </c>
       <c r="G45">
         <v>9.35</v>
@@ -4977,28 +4977,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M45">
-        <v>3.4614828</v>
+        <v>3.5419824</v>
       </c>
       <c r="N45">
-        <v>3.78586413877551</v>
+        <v>3.70536453877551</v>
       </c>
       <c r="O45">
-        <v>0.7193141863673469</v>
+        <v>0.704019262367347</v>
       </c>
       <c r="P45">
-        <v>3.066549952408163</v>
+        <v>3.001345276408163</v>
       </c>
       <c r="Q45">
-        <v>9.186549952408164</v>
+        <v>9.121345276408164</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1059882472183447</v>
+        <v>0.1069362816345575</v>
       </c>
       <c r="T45">
-        <v>1.173180966611173</v>
+        <v>1.191659921958692</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.093711671418824</v>
+        <v>2.046127315250214</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08689943771535222</v>
+        <v>0.0869844345162479</v>
       </c>
       <c r="C46">
-        <v>52.54409138346507</v>
+        <v>51.34657871608834</v>
       </c>
       <c r="D46">
-        <v>89.92209138346507</v>
+        <v>89.78657871608834</v>
       </c>
       <c r="E46">
-        <v>22.62799999999999</v>
+        <v>23.69</v>
       </c>
       <c r="F46">
-        <v>46.72799999999999</v>
+        <v>47.79</v>
       </c>
       <c r="G46">
         <v>9.35</v>
@@ -5059,28 +5059,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M46">
-        <v>3.5419824</v>
+        <v>3.622482</v>
       </c>
       <c r="N46">
-        <v>3.70536453877551</v>
+        <v>3.62486493877551</v>
       </c>
       <c r="O46">
-        <v>0.704019262367347</v>
+        <v>0.6887243383673469</v>
       </c>
       <c r="P46">
-        <v>3.001345276408163</v>
+        <v>2.936140600408163</v>
       </c>
       <c r="Q46">
-        <v>9.121345276408164</v>
+        <v>9.056140600408163</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1069362816345575</v>
+        <v>0.1079187900295416</v>
       </c>
       <c r="T46">
-        <v>1.191659921958692</v>
+        <v>1.210810839318847</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.046127315250214</v>
+        <v>2.000657819355765</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0869844345162479</v>
+        <v>0.09236035131714364</v>
       </c>
       <c r="C47">
-        <v>51.34657871608834</v>
+        <v>42.47125802341058</v>
       </c>
       <c r="D47">
-        <v>89.78657871608834</v>
+        <v>81.97325802341058</v>
       </c>
       <c r="E47">
-        <v>23.69</v>
+        <v>24.752</v>
       </c>
       <c r="F47">
-        <v>47.79</v>
+        <v>48.852</v>
       </c>
       <c r="G47">
         <v>9.35</v>
@@ -5141,45 +5141,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M47">
-        <v>3.622482</v>
+        <v>4.39668</v>
       </c>
       <c r="N47">
-        <v>3.62486493877551</v>
+        <v>2.85066693877551</v>
       </c>
       <c r="O47">
-        <v>0.6887243383673469</v>
+        <v>0.5416267183673469</v>
       </c>
       <c r="P47">
-        <v>2.936140600408163</v>
+        <v>2.309040220408163</v>
       </c>
       <c r="Q47">
-        <v>9.056140600408163</v>
+        <v>8.429040220408163</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1079187900295416</v>
+        <v>0.1089376876243401</v>
       </c>
       <c r="T47">
-        <v>1.210810839318847</v>
+        <v>1.230671049914563</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.19</v>
       </c>
       <c r="W47">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.000657819355765</v>
+        <v>1.648368072903989</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09236035131714364</v>
+        <v>0.09256036811803935</v>
       </c>
       <c r="C48">
-        <v>42.47125802341058</v>
+        <v>41.14470878702486</v>
       </c>
       <c r="D48">
-        <v>81.97325802341058</v>
+        <v>81.70870878702486</v>
       </c>
       <c r="E48">
-        <v>24.752</v>
+        <v>25.81399999999999</v>
       </c>
       <c r="F48">
-        <v>48.852</v>
+        <v>49.91399999999999</v>
       </c>
       <c r="G48">
         <v>9.35</v>
@@ -5223,28 +5223,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M48">
-        <v>4.39668</v>
+        <v>4.492259999999999</v>
       </c>
       <c r="N48">
-        <v>2.85066693877551</v>
+        <v>2.755086938775511</v>
       </c>
       <c r="O48">
-        <v>0.5416267183673469</v>
+        <v>0.5234665183673471</v>
       </c>
       <c r="P48">
-        <v>2.309040220408163</v>
+        <v>2.231620420408164</v>
       </c>
       <c r="Q48">
-        <v>8.429040220408163</v>
+        <v>8.351620420408164</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1089376876243401</v>
+        <v>0.1099950341849799</v>
       </c>
       <c r="T48">
-        <v>1.230671049914563</v>
+        <v>1.251280702419552</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.648368072903989</v>
+        <v>1.613296411778372</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09256036811803935</v>
+        <v>0.09276038491893507</v>
       </c>
       <c r="C49">
-        <v>41.14470878702486</v>
+        <v>39.81986159744227</v>
       </c>
       <c r="D49">
-        <v>81.70870878702486</v>
+        <v>81.44586159744227</v>
       </c>
       <c r="E49">
-        <v>25.81399999999999</v>
+        <v>26.876</v>
       </c>
       <c r="F49">
-        <v>49.91399999999999</v>
+        <v>50.976</v>
       </c>
       <c r="G49">
         <v>9.35</v>
@@ -5305,28 +5305,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M49">
-        <v>4.492259999999999</v>
+        <v>4.58784</v>
       </c>
       <c r="N49">
-        <v>2.755086938775511</v>
+        <v>2.65950693877551</v>
       </c>
       <c r="O49">
-        <v>0.5234665183673471</v>
+        <v>0.505306318367347</v>
       </c>
       <c r="P49">
-        <v>2.231620420408164</v>
+        <v>2.154200620408163</v>
       </c>
       <c r="Q49">
-        <v>8.351620420408164</v>
+        <v>8.274200620408163</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1099950341849799</v>
+        <v>0.1110930479210289</v>
       </c>
       <c r="T49">
-        <v>1.251280702419552</v>
+        <v>1.272683033867041</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.613296411778372</v>
+        <v>1.579686069866323</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09276038491893505</v>
+        <v>0.09296040171983075</v>
       </c>
       <c r="C50">
-        <v>39.8198615974423</v>
+        <v>38.49670008148757</v>
       </c>
       <c r="D50">
-        <v>81.4458615974423</v>
+        <v>81.18470008148758</v>
       </c>
       <c r="E50">
-        <v>26.87599999999999</v>
+        <v>27.938</v>
       </c>
       <c r="F50">
-        <v>50.97599999999999</v>
+        <v>52.038</v>
       </c>
       <c r="G50">
         <v>9.35</v>
@@ -5387,28 +5387,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M50">
-        <v>4.587839999999999</v>
+        <v>4.68342</v>
       </c>
       <c r="N50">
-        <v>2.659506938775511</v>
+        <v>2.56392693877551</v>
       </c>
       <c r="O50">
-        <v>0.5053063183673471</v>
+        <v>0.4871461183673469</v>
       </c>
       <c r="P50">
-        <v>2.154200620408164</v>
+        <v>2.076780820408163</v>
       </c>
       <c r="Q50">
-        <v>8.274200620408164</v>
+        <v>8.196780820408163</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1110930479210289</v>
+        <v>0.112234121019276</v>
       </c>
       <c r="T50">
-        <v>1.27268303386704</v>
+        <v>1.294924672430116</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.579686069866323</v>
+        <v>1.547447578644561</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09296040171983075</v>
+        <v>0.09316041852072648</v>
       </c>
       <c r="C51">
-        <v>38.49670008148757</v>
+        <v>37.17520807532077</v>
       </c>
       <c r="D51">
-        <v>81.18470008148758</v>
+        <v>80.92520807532077</v>
       </c>
       <c r="E51">
-        <v>27.938</v>
+        <v>28.99999999999999</v>
       </c>
       <c r="F51">
-        <v>52.038</v>
+        <v>53.09999999999999</v>
       </c>
       <c r="G51">
         <v>9.35</v>
@@ -5469,28 +5469,28 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M51">
-        <v>4.68342</v>
+        <v>4.778999999999999</v>
       </c>
       <c r="N51">
-        <v>2.56392693877551</v>
+        <v>2.468346938775511</v>
       </c>
       <c r="O51">
-        <v>0.4871461183673469</v>
+        <v>0.4689859183673471</v>
       </c>
       <c r="P51">
-        <v>2.076780820408163</v>
+        <v>1.999361020408164</v>
       </c>
       <c r="Q51">
-        <v>8.196780820408163</v>
+        <v>8.119361020408164</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.112234121019276</v>
+        <v>0.1134208370414529</v>
       </c>
       <c r="T51">
-        <v>1.294924672430116</v>
+        <v>1.318055976535716</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.547447578644561</v>
+        <v>1.51649862707167</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09316041852072648</v>
+        <v>0.1184037423402231</v>
       </c>
       <c r="C52">
-        <v>37.17520807532077</v>
+        <v>12.85191017945566</v>
       </c>
       <c r="D52">
-        <v>80.92520807532077</v>
+        <v>57.66391017945566</v>
       </c>
       <c r="E52">
-        <v>28.99999999999999</v>
+        <v>30.06199999999999</v>
       </c>
       <c r="F52">
-        <v>53.09999999999999</v>
+        <v>54.16199999999999</v>
       </c>
       <c r="G52">
         <v>9.35</v>
@@ -5551,45 +5551,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M52">
-        <v>4.778999999999999</v>
+        <v>7.9509816</v>
       </c>
       <c r="N52">
-        <v>2.468346938775511</v>
+        <v>-0.7036346612244895</v>
       </c>
       <c r="O52">
-        <v>0.4689859183673471</v>
+        <v>-0.133690585632653</v>
       </c>
       <c r="P52">
-        <v>1.999361020408164</v>
+        <v>-0.5699440755918365</v>
       </c>
       <c r="Q52">
-        <v>8.119361020408164</v>
+        <v>5.550055924408164</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1134208370414529</v>
+        <v>0.1153098073503793</v>
       </c>
       <c r="T52">
-        <v>1.318055976535716</v>
+        <v>1.354875523795278</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.19</v>
+        <v>0.1731856502305762</v>
       </c>
       <c r="W52">
-        <v>0.07290000000000001</v>
+        <v>0.1213763465461514</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.51649862707167</v>
+        <v>0.9115034222661904</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1184037423402231</v>
+        <v>0.1194137423402231</v>
       </c>
       <c r="C53">
-        <v>12.85191017945566</v>
+        <v>11.13427409668071</v>
       </c>
       <c r="D53">
-        <v>57.66391017945566</v>
+        <v>57.00827409668071</v>
       </c>
       <c r="E53">
-        <v>30.06199999999999</v>
+        <v>31.124</v>
       </c>
       <c r="F53">
-        <v>54.16199999999999</v>
+        <v>55.224</v>
       </c>
       <c r="G53">
         <v>9.35</v>
@@ -5633,37 +5633,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M53">
-        <v>7.9509816</v>
+        <v>8.1068832</v>
       </c>
       <c r="N53">
-        <v>-0.7036346612244895</v>
+        <v>-0.8595362612244903</v>
       </c>
       <c r="O53">
-        <v>-0.133690585632653</v>
+        <v>-0.1633118896326532</v>
       </c>
       <c r="P53">
-        <v>-0.5699440755918365</v>
+        <v>-0.6962243715918371</v>
       </c>
       <c r="Q53">
-        <v>5.550055924408164</v>
+        <v>5.423775628408163</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1153098073503793</v>
+        <v>0.1167579283368456</v>
       </c>
       <c r="T53">
-        <v>1.354875523795278</v>
+        <v>1.38310209720768</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1731856502305762</v>
+        <v>0.1698551569569112</v>
       </c>
       <c r="W53">
-        <v>0.1213763465461514</v>
+        <v>0.1218652629587254</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9115034222661904</v>
+        <v>0.8939745102995328</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1194137423402231</v>
+        <v>0.1204237423402231</v>
       </c>
       <c r="C54">
-        <v>11.13427409668071</v>
+        <v>9.431379509702175</v>
       </c>
       <c r="D54">
-        <v>57.00827409668071</v>
+        <v>56.36737950970217</v>
       </c>
       <c r="E54">
-        <v>31.124</v>
+        <v>32.18599999999999</v>
       </c>
       <c r="F54">
-        <v>55.224</v>
+        <v>56.28599999999999</v>
       </c>
       <c r="G54">
         <v>9.35</v>
@@ -5715,37 +5715,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M54">
-        <v>8.1068832</v>
+        <v>8.2627848</v>
       </c>
       <c r="N54">
-        <v>-0.8595362612244903</v>
+        <v>-1.01543786122449</v>
       </c>
       <c r="O54">
-        <v>-0.1633118896326532</v>
+        <v>-0.1929331936326532</v>
       </c>
       <c r="P54">
-        <v>-0.6962243715918371</v>
+        <v>-0.8225046675918372</v>
       </c>
       <c r="Q54">
-        <v>5.423775628408163</v>
+        <v>5.297495332408163</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1167579283368456</v>
+        <v>0.1182676714929487</v>
       </c>
       <c r="T54">
-        <v>1.38310209720768</v>
+        <v>1.412529801403588</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1698551569569112</v>
+        <v>0.1666503426747054</v>
       </c>
       <c r="W54">
-        <v>0.1218652629587254</v>
+        <v>0.1223357296953533</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8939745102995328</v>
+        <v>0.8771070667089756</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1204237423402231</v>
+        <v>0.1214337423402231</v>
       </c>
       <c r="C55">
-        <v>9.431379509702175</v>
+        <v>7.742734768159309</v>
       </c>
       <c r="D55">
-        <v>56.36737950970217</v>
+        <v>55.74073476815931</v>
       </c>
       <c r="E55">
-        <v>32.18599999999999</v>
+        <v>33.248</v>
       </c>
       <c r="F55">
-        <v>56.28599999999999</v>
+        <v>57.348</v>
       </c>
       <c r="G55">
         <v>9.35</v>
@@ -5797,37 +5797,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M55">
-        <v>8.2627848</v>
+        <v>8.4186864</v>
       </c>
       <c r="N55">
-        <v>-1.01543786122449</v>
+        <v>-1.17133946122449</v>
       </c>
       <c r="O55">
-        <v>-0.1929331936326532</v>
+        <v>-0.2225544976326532</v>
       </c>
       <c r="P55">
-        <v>-0.8225046675918372</v>
+        <v>-0.9487849635918371</v>
       </c>
       <c r="Q55">
-        <v>5.297495332408163</v>
+        <v>5.171215036408163</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1182676714929487</v>
+        <v>0.1198430556558388</v>
       </c>
       <c r="T55">
-        <v>1.412529801403588</v>
+        <v>1.443236970999318</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1666503426747054</v>
+        <v>0.1635642252177664</v>
       </c>
       <c r="W55">
-        <v>0.1223357296953533</v>
+        <v>0.1227887717380319</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8771070667089756</v>
+        <v>0.860864343251402</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1214337423402231</v>
+        <v>0.1224437423402231</v>
       </c>
       <c r="C56">
-        <v>7.742734768159309</v>
+        <v>6.06786984431703</v>
       </c>
       <c r="D56">
-        <v>55.74073476815931</v>
+        <v>55.12786984431703</v>
       </c>
       <c r="E56">
-        <v>33.248</v>
+        <v>34.31</v>
       </c>
       <c r="F56">
-        <v>57.348</v>
+        <v>58.41</v>
       </c>
       <c r="G56">
         <v>9.35</v>
@@ -5879,37 +5879,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M56">
-        <v>8.4186864</v>
+        <v>8.574588</v>
       </c>
       <c r="N56">
-        <v>-1.17133946122449</v>
+        <v>-1.32724106122449</v>
       </c>
       <c r="O56">
-        <v>-0.2225544976326532</v>
+        <v>-0.2521758016326531</v>
       </c>
       <c r="P56">
-        <v>-0.9487849635918371</v>
+        <v>-1.075065259591837</v>
       </c>
       <c r="Q56">
-        <v>5.171215036408163</v>
+        <v>5.044934740408163</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1198430556558388</v>
+        <v>0.1214884568926353</v>
       </c>
       <c r="T56">
-        <v>1.443236970999318</v>
+        <v>1.475308903688191</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1635642252177664</v>
+        <v>0.160590330213807</v>
       </c>
       <c r="W56">
-        <v>0.1227887717380319</v>
+        <v>0.1232253395246131</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.860864343251402</v>
+        <v>0.8452122642831947</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1224437423402231</v>
+        <v>0.1234537423402231</v>
       </c>
       <c r="C57">
-        <v>6.06786984431703</v>
+        <v>4.406335157298287</v>
       </c>
       <c r="D57">
-        <v>55.12786984431703</v>
+        <v>54.52833515729829</v>
       </c>
       <c r="E57">
-        <v>34.31</v>
+        <v>35.372</v>
       </c>
       <c r="F57">
-        <v>58.41</v>
+        <v>59.472</v>
       </c>
       <c r="G57">
         <v>9.35</v>
@@ -5961,37 +5961,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M57">
-        <v>8.574588</v>
+        <v>8.7304896</v>
       </c>
       <c r="N57">
-        <v>-1.32724106122449</v>
+        <v>-1.48314266122449</v>
       </c>
       <c r="O57">
-        <v>-0.2521758016326531</v>
+        <v>-0.2817971056326531</v>
       </c>
       <c r="P57">
-        <v>-1.075065259591837</v>
+        <v>-1.201345555591837</v>
       </c>
       <c r="Q57">
-        <v>5.044934740408163</v>
+        <v>4.918654444408163</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1214884568926353</v>
+        <v>0.1232086490947406</v>
       </c>
       <c r="T57">
-        <v>1.475308903688191</v>
+        <v>1.508838651499287</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.160590330213807</v>
+        <v>0.1577226457457033</v>
       </c>
       <c r="W57">
-        <v>0.1232253395246131</v>
+        <v>0.1236463156045308</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8452122642831947</v>
+        <v>0.8301191881352805</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1234537423402231</v>
+        <v>0.1244637423402231</v>
       </c>
       <c r="C58">
-        <v>4.406335157298287</v>
+        <v>2.757700473212104</v>
       </c>
       <c r="D58">
-        <v>54.52833515729829</v>
+        <v>53.9417004732121</v>
       </c>
       <c r="E58">
-        <v>35.372</v>
+        <v>36.434</v>
       </c>
       <c r="F58">
-        <v>59.472</v>
+        <v>60.534</v>
       </c>
       <c r="G58">
         <v>9.35</v>
@@ -6043,37 +6043,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M58">
-        <v>8.7304896</v>
+        <v>8.8863912</v>
       </c>
       <c r="N58">
-        <v>-1.48314266122449</v>
+        <v>-1.63904426122449</v>
       </c>
       <c r="O58">
-        <v>-0.2817971056326531</v>
+        <v>-0.3114184096326532</v>
       </c>
       <c r="P58">
-        <v>-1.201345555591837</v>
+        <v>-1.327625851591837</v>
       </c>
       <c r="Q58">
-        <v>4.918654444408163</v>
+        <v>4.792374148408163</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1232086490947406</v>
+        <v>0.1250088502364788</v>
       </c>
       <c r="T58">
-        <v>1.508838651499287</v>
+        <v>1.543927922464386</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1577226457457033</v>
+        <v>0.1549555817852524</v>
       </c>
       <c r="W58">
-        <v>0.1236463156045308</v>
+        <v>0.124052520593925</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8301191881352805</v>
+        <v>0.8155556936065914</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1244637423402231</v>
+        <v>0.1254737423402231</v>
       </c>
       <c r="C59">
-        <v>2.757700473212104</v>
+        <v>1.121553875522864</v>
       </c>
       <c r="D59">
-        <v>53.9417004732121</v>
+        <v>53.36755387552287</v>
       </c>
       <c r="E59">
-        <v>36.434</v>
+        <v>37.496</v>
       </c>
       <c r="F59">
-        <v>60.534</v>
+        <v>61.596</v>
       </c>
       <c r="G59">
         <v>9.35</v>
@@ -6125,37 +6125,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M59">
-        <v>8.8863912</v>
+        <v>9.042292800000002</v>
       </c>
       <c r="N59">
-        <v>-1.63904426122449</v>
+        <v>-1.794945861224492</v>
       </c>
       <c r="O59">
-        <v>-0.3114184096326532</v>
+        <v>-0.3410397136326535</v>
       </c>
       <c r="P59">
-        <v>-1.327625851591837</v>
+        <v>-1.453906147591838</v>
       </c>
       <c r="Q59">
-        <v>4.792374148408163</v>
+        <v>4.666093852408162</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1250088502364788</v>
+        <v>0.1268947752421092</v>
       </c>
       <c r="T59">
-        <v>1.543927922464386</v>
+        <v>1.580688111094491</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1549555817852524</v>
+        <v>0.1522839338234376</v>
       </c>
       <c r="W59">
-        <v>0.124052520593925</v>
+        <v>0.1244447185147194</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8155556936065914</v>
+        <v>0.8014943885444086</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1254737423402231</v>
+        <v>0.1592311314597936</v>
       </c>
       <c r="C60">
-        <v>1.121553875522892</v>
+        <v>-13.94415685409635</v>
       </c>
       <c r="D60">
-        <v>53.36755387552288</v>
+        <v>39.36384314590364</v>
       </c>
       <c r="E60">
-        <v>37.49599999999999</v>
+        <v>38.55799999999999</v>
       </c>
       <c r="F60">
-        <v>61.59599999999999</v>
+        <v>62.65799999999999</v>
       </c>
       <c r="G60">
         <v>9.35</v>
@@ -6207,45 +6207,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M60">
-        <v>9.042292799999998</v>
+        <v>12.5817264</v>
       </c>
       <c r="N60">
-        <v>-1.794945861224488</v>
+        <v>-5.334379461224487</v>
       </c>
       <c r="O60">
-        <v>-0.3410397136326528</v>
+        <v>-1.013532097632653</v>
       </c>
       <c r="P60">
-        <v>-1.453906147591836</v>
+        <v>-4.320847363591835</v>
       </c>
       <c r="Q60">
-        <v>4.666093852408165</v>
+        <v>1.799152636408166</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1268947752421092</v>
+        <v>0.1310370602957474</v>
       </c>
       <c r="T60">
-        <v>1.58068811109449</v>
+        <v>1.661428956821015</v>
       </c>
       <c r="U60">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1522839338234377</v>
+        <v>0.1094441155839589</v>
       </c>
       <c r="W60">
-        <v>0.1244447185147194</v>
+        <v>0.1788236215907411</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8014943885444089</v>
+        <v>0.5760216609682047</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1592311314597936</v>
+        <v>0.1607811314597937</v>
       </c>
       <c r="C61">
-        <v>-13.94415685409635</v>
+        <v>-15.47478125745836</v>
       </c>
       <c r="D61">
-        <v>39.36384314590364</v>
+        <v>38.89521874254163</v>
       </c>
       <c r="E61">
-        <v>38.55799999999999</v>
+        <v>39.61999999999999</v>
       </c>
       <c r="F61">
-        <v>62.65799999999999</v>
+        <v>63.71999999999999</v>
       </c>
       <c r="G61">
         <v>9.35</v>
@@ -6289,37 +6289,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M61">
-        <v>12.5817264</v>
+        <v>12.794976</v>
       </c>
       <c r="N61">
-        <v>-5.334379461224487</v>
+        <v>-5.547629061224488</v>
       </c>
       <c r="O61">
-        <v>-1.013532097632653</v>
+        <v>-1.054049521632653</v>
       </c>
       <c r="P61">
-        <v>-4.320847363591835</v>
+        <v>-4.493579539591836</v>
       </c>
       <c r="Q61">
-        <v>1.799152636408166</v>
+        <v>1.626420460408164</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1310370602957474</v>
+        <v>0.1331679868031411</v>
       </c>
       <c r="T61">
-        <v>1.661428956821015</v>
+        <v>1.70296468074154</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1094441155839589</v>
+        <v>0.1076200469908929</v>
       </c>
       <c r="W61">
-        <v>0.1788236215907411</v>
+        <v>0.1791898945642287</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5760216609682047</v>
+        <v>0.5664212999520679</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1607811314597937</v>
+        <v>0.1623311314597936</v>
       </c>
       <c r="C62">
-        <v>-15.47478125745836</v>
+        <v>-16.99437903631336</v>
       </c>
       <c r="D62">
-        <v>38.89521874254163</v>
+        <v>38.43762096368663</v>
       </c>
       <c r="E62">
-        <v>39.61999999999999</v>
+        <v>40.682</v>
       </c>
       <c r="F62">
-        <v>63.71999999999999</v>
+        <v>64.782</v>
       </c>
       <c r="G62">
         <v>9.35</v>
@@ -6371,37 +6371,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M62">
-        <v>12.794976</v>
+        <v>13.0082256</v>
       </c>
       <c r="N62">
-        <v>-5.547629061224488</v>
+        <v>-5.760878661224489</v>
       </c>
       <c r="O62">
-        <v>-1.054049521632653</v>
+        <v>-1.094566945632653</v>
       </c>
       <c r="P62">
-        <v>-4.493579539591836</v>
+        <v>-4.666311715591837</v>
       </c>
       <c r="Q62">
-        <v>1.626420460408164</v>
+        <v>1.453688284408163</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1331679868031411</v>
+        <v>0.1354081915929652</v>
       </c>
       <c r="T62">
-        <v>1.70296468074154</v>
+        <v>1.746630441786195</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1076200469908929</v>
+        <v>0.1058557839254684</v>
       </c>
       <c r="W62">
-        <v>0.1791898945642287</v>
+        <v>0.1795441585877659</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5664212999520679</v>
+        <v>0.5571357048708865</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1623311314597936</v>
+        <v>0.1638811314597937</v>
       </c>
       <c r="C63">
-        <v>-16.99437903631336</v>
+        <v>-18.50333484614442</v>
       </c>
       <c r="D63">
-        <v>38.43762096368663</v>
+        <v>37.99066515385557</v>
       </c>
       <c r="E63">
-        <v>40.682</v>
+        <v>41.74399999999999</v>
       </c>
       <c r="F63">
-        <v>64.782</v>
+        <v>65.84399999999999</v>
       </c>
       <c r="G63">
         <v>9.35</v>
@@ -6453,37 +6453,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M63">
-        <v>13.0082256</v>
+        <v>13.2214752</v>
       </c>
       <c r="N63">
-        <v>-5.760878661224489</v>
+        <v>-5.974128261224489</v>
       </c>
       <c r="O63">
-        <v>-1.094566945632653</v>
+        <v>-1.135084369632653</v>
       </c>
       <c r="P63">
-        <v>-4.666311715591837</v>
+        <v>-4.839043891591835</v>
       </c>
       <c r="Q63">
-        <v>1.453688284408163</v>
+        <v>1.280956108408165</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1354081915929652</v>
+        <v>0.1377663018980432</v>
       </c>
       <c r="T63">
-        <v>1.746630441786195</v>
+        <v>1.792594400780569</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1058557839254684</v>
+        <v>0.1041484325718319</v>
       </c>
       <c r="W63">
-        <v>0.1795441585877659</v>
+        <v>0.1798869947395762</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5571357048708865</v>
+        <v>0.5481496451149045</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1638811314597937</v>
+        <v>0.1654311314597937</v>
       </c>
       <c r="C64">
-        <v>-18.50333484614442</v>
+        <v>-20.00201565686179</v>
       </c>
       <c r="D64">
-        <v>37.99066515385557</v>
+        <v>37.5539843431382</v>
       </c>
       <c r="E64">
-        <v>41.74399999999999</v>
+        <v>42.80599999999999</v>
       </c>
       <c r="F64">
-        <v>65.84399999999999</v>
+        <v>66.90599999999999</v>
       </c>
       <c r="G64">
         <v>9.35</v>
@@ -6535,37 +6535,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M64">
-        <v>13.2214752</v>
+        <v>13.4347248</v>
       </c>
       <c r="N64">
-        <v>-5.974128261224489</v>
+        <v>-6.187377861224488</v>
       </c>
       <c r="O64">
-        <v>-1.135084369632653</v>
+        <v>-1.175601793632653</v>
       </c>
       <c r="P64">
-        <v>-4.839043891591835</v>
+        <v>-5.011776067591835</v>
       </c>
       <c r="Q64">
-        <v>1.280956108408165</v>
+        <v>1.108223932408165</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1377663018980432</v>
+        <v>0.1402518776250174</v>
       </c>
       <c r="T64">
-        <v>1.792594400780569</v>
+        <v>1.841042898098962</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1041484325718319</v>
+        <v>0.1024952828484694</v>
       </c>
       <c r="W64">
-        <v>0.1798869947395762</v>
+        <v>0.1802189472040273</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5481496451149045</v>
+        <v>0.5394488570972076</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1654311314597937</v>
+        <v>0.1669811314597937</v>
       </c>
       <c r="C65">
-        <v>-20.00201565686179</v>
+        <v>-21.49077175767989</v>
       </c>
       <c r="D65">
-        <v>37.5539843431382</v>
+        <v>37.12722824232009</v>
       </c>
       <c r="E65">
-        <v>42.80599999999999</v>
+        <v>43.86799999999999</v>
       </c>
       <c r="F65">
-        <v>66.90599999999999</v>
+        <v>67.96799999999999</v>
       </c>
       <c r="G65">
         <v>9.35</v>
@@ -6617,37 +6617,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M65">
-        <v>13.4347248</v>
+        <v>13.6479744</v>
       </c>
       <c r="N65">
-        <v>-6.187377861224488</v>
+        <v>-6.400627461224489</v>
       </c>
       <c r="O65">
-        <v>-1.175601793632653</v>
+        <v>-1.216119217632653</v>
       </c>
       <c r="P65">
-        <v>-5.011776067591835</v>
+        <v>-5.184508243591836</v>
       </c>
       <c r="Q65">
-        <v>1.108223932408165</v>
+        <v>0.9354917564081644</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1402518776250174</v>
+        <v>0.142875540892379</v>
       </c>
       <c r="T65">
-        <v>1.841042898098962</v>
+        <v>1.892182978601711</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1024952828484694</v>
+        <v>0.1008937940539621</v>
       </c>
       <c r="W65">
-        <v>0.1802189472040273</v>
+        <v>0.1805405261539644</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5394488570972076</v>
+        <v>0.5310199687050636</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1669811314597937</v>
+        <v>0.1685311314597936</v>
       </c>
       <c r="C66">
-        <v>-21.49077175767989</v>
+        <v>-22.96993769424862</v>
       </c>
       <c r="D66">
-        <v>37.12722824232009</v>
+        <v>36.71006230575138</v>
       </c>
       <c r="E66">
-        <v>43.86799999999999</v>
+        <v>44.93</v>
       </c>
       <c r="F66">
-        <v>67.96799999999999</v>
+        <v>69.03</v>
       </c>
       <c r="G66">
         <v>9.35</v>
@@ -6699,37 +6699,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M66">
-        <v>13.6479744</v>
+        <v>13.861224</v>
       </c>
       <c r="N66">
-        <v>-6.400627461224489</v>
+        <v>-6.61387706122449</v>
       </c>
       <c r="O66">
-        <v>-1.216119217632653</v>
+        <v>-1.256636641632653</v>
       </c>
       <c r="P66">
-        <v>-5.184508243591836</v>
+        <v>-5.357240419591837</v>
       </c>
       <c r="Q66">
-        <v>0.9354917564081644</v>
+        <v>0.7627595804081633</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.142875540892379</v>
+        <v>0.1456491277750184</v>
       </c>
       <c r="T66">
-        <v>1.892182978601711</v>
+        <v>1.946245349418903</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1008937940539621</v>
+        <v>0.09934158183774729</v>
       </c>
       <c r="W66">
-        <v>0.1805405261539644</v>
+        <v>0.1808522103669803</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5310199687050636</v>
+        <v>0.5228504307249857</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1685311314597936</v>
+        <v>0.1700811314597936</v>
       </c>
       <c r="C67">
-        <v>-22.96993769424862</v>
+        <v>-24.43983314330838</v>
       </c>
       <c r="D67">
-        <v>36.71006230575138</v>
+        <v>36.30216685669162</v>
       </c>
       <c r="E67">
-        <v>44.93</v>
+        <v>45.992</v>
       </c>
       <c r="F67">
-        <v>69.03</v>
+        <v>70.092</v>
       </c>
       <c r="G67">
         <v>9.35</v>
@@ -6781,37 +6781,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M67">
-        <v>13.861224</v>
+        <v>14.0744736</v>
       </c>
       <c r="N67">
-        <v>-6.61387706122449</v>
+        <v>-6.827126661224491</v>
       </c>
       <c r="O67">
-        <v>-1.256636641632653</v>
+        <v>-1.297154065632653</v>
       </c>
       <c r="P67">
-        <v>-5.357240419591837</v>
+        <v>-5.529972595591838</v>
       </c>
       <c r="Q67">
-        <v>0.7627595804081633</v>
+        <v>0.5900274044081621</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1456491277750184</v>
+        <v>0.1485858668272248</v>
       </c>
       <c r="T67">
-        <v>1.946245349418903</v>
+        <v>2.00348785969593</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.09934158183774729</v>
+        <v>0.09783640635535718</v>
       </c>
       <c r="W67">
-        <v>0.1808522103669803</v>
+        <v>0.1811544496038443</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5228504307249857</v>
+        <v>0.51492845450188</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1700811314597936</v>
+        <v>0.1716311314597937</v>
       </c>
       <c r="C68">
-        <v>-24.43983314330838</v>
+        <v>-25.90076372967484</v>
       </c>
       <c r="D68">
-        <v>36.30216685669162</v>
+        <v>35.90323627032515</v>
       </c>
       <c r="E68">
-        <v>45.992</v>
+        <v>47.05399999999999</v>
       </c>
       <c r="F68">
-        <v>70.092</v>
+        <v>71.154</v>
       </c>
       <c r="G68">
         <v>9.35</v>
@@ -6863,37 +6863,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M68">
-        <v>14.0744736</v>
+        <v>14.2877232</v>
       </c>
       <c r="N68">
-        <v>-6.827126661224491</v>
+        <v>-7.04037626122449</v>
       </c>
       <c r="O68">
-        <v>-1.297154065632653</v>
+        <v>-1.337671489632653</v>
       </c>
       <c r="P68">
-        <v>-5.529972595591838</v>
+        <v>-5.702704771591837</v>
       </c>
       <c r="Q68">
-        <v>0.5900274044081621</v>
+        <v>0.4172952284081628</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1485858668272248</v>
+        <v>0.1517005900644134</v>
       </c>
       <c r="T68">
-        <v>2.00348785969593</v>
+        <v>2.064199613020049</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09783640635535718</v>
+        <v>0.0963761614843817</v>
       </c>
       <c r="W68">
-        <v>0.1811544496038443</v>
+        <v>0.1814476667739362</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.51492845450188</v>
+        <v>0.5072429551809563</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1716311314597937</v>
+        <v>0.1973392036880123</v>
       </c>
       <c r="C69">
-        <v>-25.90076372967484</v>
+        <v>-32.4978127185467</v>
       </c>
       <c r="D69">
-        <v>35.90323627032515</v>
+        <v>30.3681872814533</v>
       </c>
       <c r="E69">
-        <v>47.05399999999999</v>
+        <v>48.11599999999999</v>
       </c>
       <c r="F69">
-        <v>71.154</v>
+        <v>72.21599999999999</v>
       </c>
       <c r="G69">
         <v>9.35</v>
@@ -6945,45 +6945,45 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M69">
-        <v>14.2877232</v>
+        <v>17.0285328</v>
       </c>
       <c r="N69">
-        <v>-7.04037626122449</v>
+        <v>-9.78118586122449</v>
       </c>
       <c r="O69">
-        <v>-1.337671489632653</v>
+        <v>-1.858425313632653</v>
       </c>
       <c r="P69">
-        <v>-5.702704771591837</v>
+        <v>-7.922760547591837</v>
       </c>
       <c r="Q69">
-        <v>0.4172952284081628</v>
+        <v>-1.802760547591837</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1517005900644134</v>
+        <v>0.1561289592171096</v>
       </c>
       <c r="T69">
-        <v>2.064199613020049</v>
+        <v>2.150516770325266</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0963761614843817</v>
+        <v>0.08086403770308073</v>
       </c>
       <c r="W69">
-        <v>0.1814476667739362</v>
+        <v>0.2167322599096136</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5072429551809563</v>
+        <v>0.425600198437267</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1973392036880123</v>
+        <v>0.1992392036880123</v>
       </c>
       <c r="C70">
-        <v>-32.4978127185467</v>
+        <v>-33.90192644978272</v>
       </c>
       <c r="D70">
-        <v>30.3681872814533</v>
+        <v>30.02607355021727</v>
       </c>
       <c r="E70">
-        <v>48.11599999999999</v>
+        <v>49.17799999999999</v>
       </c>
       <c r="F70">
-        <v>72.21599999999999</v>
+        <v>73.27799999999999</v>
       </c>
       <c r="G70">
         <v>9.35</v>
@@ -7027,37 +7027,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M70">
-        <v>17.0285328</v>
+        <v>17.2789524</v>
       </c>
       <c r="N70">
-        <v>-9.78118586122449</v>
+        <v>-10.03160546122449</v>
       </c>
       <c r="O70">
-        <v>-1.858425313632653</v>
+        <v>-1.906005037632652</v>
       </c>
       <c r="P70">
-        <v>-7.922760547591837</v>
+        <v>-8.125600423591834</v>
       </c>
       <c r="Q70">
-        <v>-1.802760547591837</v>
+        <v>-2.005600423591834</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1561289592171096</v>
+        <v>0.1596879579015325</v>
       </c>
       <c r="T70">
-        <v>2.150516770325266</v>
+        <v>2.219888279045437</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08086403770308073</v>
+        <v>0.07969209512767378</v>
       </c>
       <c r="W70">
-        <v>0.2167322599096136</v>
+        <v>0.2170086039688945</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.425600198437267</v>
+        <v>0.4194320796193357</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1992392036880123</v>
+        <v>0.2011392036880123</v>
       </c>
       <c r="C71">
-        <v>-33.90192644978272</v>
+        <v>-35.29841786529794</v>
       </c>
       <c r="D71">
-        <v>30.02607355021727</v>
+        <v>29.69158213470207</v>
       </c>
       <c r="E71">
-        <v>49.17799999999999</v>
+        <v>50.24</v>
       </c>
       <c r="F71">
-        <v>73.27799999999999</v>
+        <v>74.34</v>
       </c>
       <c r="G71">
         <v>9.35</v>
@@ -7109,37 +7109,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M71">
-        <v>17.2789524</v>
+        <v>17.529372</v>
       </c>
       <c r="N71">
-        <v>-10.03160546122449</v>
+        <v>-10.28202506122449</v>
       </c>
       <c r="O71">
-        <v>-1.906005037632652</v>
+        <v>-1.953584761632653</v>
       </c>
       <c r="P71">
-        <v>-8.125600423591834</v>
+        <v>-8.328440299591838</v>
       </c>
       <c r="Q71">
-        <v>-2.005600423591834</v>
+        <v>-2.208440299591838</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1596879579015325</v>
+        <v>0.1634842231649169</v>
       </c>
       <c r="T71">
-        <v>2.219888279045437</v>
+        <v>2.293884555013618</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07969209512767378</v>
+        <v>0.07855363662584985</v>
       </c>
       <c r="W71">
-        <v>0.2170086039688945</v>
+        <v>0.2172770524836246</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4194320796193357</v>
+        <v>0.4134401927676308</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2011392036880123</v>
+        <v>0.2030392036880123</v>
       </c>
       <c r="C72">
-        <v>-35.29841786529794</v>
+        <v>-36.68753889708149</v>
       </c>
       <c r="D72">
-        <v>29.69158213470207</v>
+        <v>29.36446110291851</v>
       </c>
       <c r="E72">
-        <v>50.24</v>
+        <v>51.302</v>
       </c>
       <c r="F72">
-        <v>74.34</v>
+        <v>75.402</v>
       </c>
       <c r="G72">
         <v>9.35</v>
@@ -7191,37 +7191,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M72">
-        <v>17.529372</v>
+        <v>17.7797916</v>
       </c>
       <c r="N72">
-        <v>-10.28202506122449</v>
+        <v>-10.53244466122449</v>
       </c>
       <c r="O72">
-        <v>-1.953584761632653</v>
+        <v>-2.001164485632653</v>
       </c>
       <c r="P72">
-        <v>-8.328440299591838</v>
+        <v>-8.531280175591835</v>
       </c>
       <c r="Q72">
-        <v>-2.208440299591838</v>
+        <v>-2.411280175591835</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1634842231649169</v>
+        <v>0.1675422998257761</v>
       </c>
       <c r="T72">
-        <v>2.293884555013618</v>
+        <v>2.372984022427881</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07855363662584985</v>
+        <v>0.07744724737759845</v>
       </c>
       <c r="W72">
-        <v>0.2172770524836246</v>
+        <v>0.2175379390683623</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4134401927676308</v>
+        <v>0.4076170914610445</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2030392036880123</v>
+        <v>0.2049392036880123</v>
       </c>
       <c r="C73">
-        <v>-36.68753889708147</v>
+        <v>-38.06953049566856</v>
       </c>
       <c r="D73">
-        <v>29.36446110291851</v>
+        <v>29.04446950433143</v>
       </c>
       <c r="E73">
-        <v>51.30199999999999</v>
+        <v>52.36399999999998</v>
       </c>
       <c r="F73">
-        <v>75.40199999999999</v>
+        <v>76.46399999999998</v>
       </c>
       <c r="G73">
         <v>9.35</v>
@@ -7273,37 +7273,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M73">
-        <v>17.7797916</v>
+        <v>18.0302112</v>
       </c>
       <c r="N73">
-        <v>-10.53244466122449</v>
+        <v>-10.78286426122449</v>
       </c>
       <c r="O73">
-        <v>-2.001164485632653</v>
+        <v>-2.048744209632652</v>
       </c>
       <c r="P73">
-        <v>-8.531280175591835</v>
+        <v>-8.734120051591834</v>
       </c>
       <c r="Q73">
-        <v>-2.411280175591835</v>
+        <v>-2.614120051591834</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1675422998257761</v>
+        <v>0.1718902391052681</v>
       </c>
       <c r="T73">
-        <v>2.37298402242788</v>
+        <v>2.457733451800304</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07744724737759845</v>
+        <v>0.0763715911640207</v>
       </c>
       <c r="W73">
-        <v>0.2175379390683623</v>
+        <v>0.2177915788035239</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4076170914610445</v>
+        <v>0.4019557429685301</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2049392036880123</v>
+        <v>0.2068392036880123</v>
       </c>
       <c r="C74">
-        <v>-38.06953049566856</v>
+        <v>-39.4446232220281</v>
       </c>
       <c r="D74">
-        <v>29.04446950433143</v>
+        <v>28.7313767779719</v>
       </c>
       <c r="E74">
-        <v>52.36399999999998</v>
+        <v>53.42599999999999</v>
       </c>
       <c r="F74">
-        <v>76.46399999999998</v>
+        <v>77.526</v>
       </c>
       <c r="G74">
         <v>9.35</v>
@@ -7355,37 +7355,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M74">
-        <v>18.0302112</v>
+        <v>18.2806308</v>
       </c>
       <c r="N74">
-        <v>-10.78286426122449</v>
+        <v>-11.03328386122449</v>
       </c>
       <c r="O74">
-        <v>-2.048744209632652</v>
+        <v>-2.096323933632653</v>
       </c>
       <c r="P74">
-        <v>-8.734120051591834</v>
+        <v>-8.936959927591836</v>
       </c>
       <c r="Q74">
-        <v>-2.614120051591834</v>
+        <v>-2.816959927591836</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1718902391052681</v>
+        <v>0.1765602479610187</v>
       </c>
       <c r="T74">
-        <v>2.457733451800304</v>
+        <v>2.548760616681796</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0763715911640207</v>
+        <v>0.07532540498369164</v>
       </c>
       <c r="W74">
-        <v>0.2177915788035239</v>
+        <v>0.2180382695048455</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4019557429685301</v>
+        <v>0.3964494999141666</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2068392036880123</v>
+        <v>0.2087392036880123</v>
       </c>
       <c r="C75">
-        <v>-39.4446232220281</v>
+        <v>-40.81303780157633</v>
       </c>
       <c r="D75">
-        <v>28.7313767779719</v>
+        <v>28.42496219842367</v>
       </c>
       <c r="E75">
-        <v>53.42599999999999</v>
+        <v>54.48799999999999</v>
       </c>
       <c r="F75">
-        <v>77.526</v>
+        <v>78.58799999999999</v>
       </c>
       <c r="G75">
         <v>9.35</v>
@@ -7437,37 +7437,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M75">
-        <v>18.2806308</v>
+        <v>18.5310504</v>
       </c>
       <c r="N75">
-        <v>-11.03328386122449</v>
+        <v>-11.28370346122449</v>
       </c>
       <c r="O75">
-        <v>-2.096323933632653</v>
+        <v>-2.143903657632653</v>
       </c>
       <c r="P75">
-        <v>-8.936959927591836</v>
+        <v>-9.139799803591835</v>
       </c>
       <c r="Q75">
-        <v>-2.816959927591836</v>
+        <v>-3.019799803591835</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1765602479610187</v>
+        <v>0.1815894882672118</v>
       </c>
       <c r="T75">
-        <v>2.548760616681796</v>
+        <v>2.646789871169558</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07532540498369164</v>
+        <v>0.07430749410553365</v>
       </c>
       <c r="W75">
-        <v>0.2180382695048455</v>
+        <v>0.2182782928899152</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3964494999141666</v>
+        <v>0.3910920742396509</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2087392036880123</v>
+        <v>0.2106392036880123</v>
       </c>
       <c r="C76">
-        <v>-40.81303780157633</v>
+        <v>-42.17498564311381</v>
       </c>
       <c r="D76">
-        <v>28.42496219842367</v>
+        <v>28.12501435688618</v>
       </c>
       <c r="E76">
-        <v>54.48799999999999</v>
+        <v>55.54999999999999</v>
       </c>
       <c r="F76">
-        <v>78.58799999999999</v>
+        <v>79.64999999999999</v>
       </c>
       <c r="G76">
         <v>9.35</v>
@@ -7519,37 +7519,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M76">
-        <v>18.5310504</v>
+        <v>18.78147</v>
       </c>
       <c r="N76">
-        <v>-11.28370346122449</v>
+        <v>-11.53412306122449</v>
       </c>
       <c r="O76">
-        <v>-2.143903657632653</v>
+        <v>-2.191483381632653</v>
       </c>
       <c r="P76">
-        <v>-9.139799803591835</v>
+        <v>-9.342639679591835</v>
       </c>
       <c r="Q76">
-        <v>-3.019799803591835</v>
+        <v>-3.222639679591835</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1815894882672118</v>
+        <v>0.1870210677979003</v>
       </c>
       <c r="T76">
-        <v>2.646789871169558</v>
+        <v>2.752661466016341</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07430749410553365</v>
+        <v>0.07331672751745988</v>
       </c>
       <c r="W76">
-        <v>0.2182782928899152</v>
+        <v>0.218511915651383</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3910920742396509</v>
+        <v>0.3858775132497888</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2106392036880123</v>
+        <v>0.2125392036880123</v>
       </c>
       <c r="C77">
-        <v>-42.17498564311381</v>
+        <v>-43.53066932524975</v>
       </c>
       <c r="D77">
-        <v>28.12501435688618</v>
+        <v>27.83133067475024</v>
       </c>
       <c r="E77">
-        <v>55.54999999999999</v>
+        <v>56.61199999999999</v>
       </c>
       <c r="F77">
-        <v>79.64999999999999</v>
+        <v>80.71199999999999</v>
       </c>
       <c r="G77">
         <v>9.35</v>
@@ -7601,37 +7601,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M77">
-        <v>18.78147</v>
+        <v>19.0318896</v>
       </c>
       <c r="N77">
-        <v>-11.53412306122449</v>
+        <v>-11.78454266122449</v>
       </c>
       <c r="O77">
-        <v>-2.191483381632653</v>
+        <v>-2.239063105632653</v>
       </c>
       <c r="P77">
-        <v>-9.342639679591835</v>
+        <v>-9.545479555591836</v>
       </c>
       <c r="Q77">
-        <v>-3.222639679591835</v>
+        <v>-3.425479555591836</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1870210677979003</v>
+        <v>0.1929052789561461</v>
       </c>
       <c r="T77">
-        <v>2.752661466016341</v>
+        <v>2.867355693767022</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07331672751745988</v>
+        <v>0.07235203373433539</v>
       </c>
       <c r="W77">
-        <v>0.218511915651383</v>
+        <v>0.2187393904454437</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3858775132497888</v>
+        <v>0.3808001775491336</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2125392036880123</v>
+        <v>0.2144392036880123</v>
       </c>
       <c r="C78">
-        <v>-43.53066932524975</v>
+        <v>-44.8802830526654</v>
       </c>
       <c r="D78">
-        <v>27.83133067475024</v>
+        <v>27.54371694733459</v>
       </c>
       <c r="E78">
-        <v>56.61199999999999</v>
+        <v>57.67399999999999</v>
       </c>
       <c r="F78">
-        <v>80.71199999999999</v>
+        <v>81.77399999999999</v>
       </c>
       <c r="G78">
         <v>9.35</v>
@@ -7683,37 +7683,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M78">
-        <v>19.0318896</v>
+        <v>19.2823092</v>
       </c>
       <c r="N78">
-        <v>-11.78454266122449</v>
+        <v>-12.03496226122449</v>
       </c>
       <c r="O78">
-        <v>-2.239063105632653</v>
+        <v>-2.286642829632652</v>
       </c>
       <c r="P78">
-        <v>-9.545479555591836</v>
+        <v>-9.748319431591833</v>
       </c>
       <c r="Q78">
-        <v>-3.425479555591836</v>
+        <v>-3.628319431591833</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1929052789561461</v>
+        <v>0.1993011606498916</v>
       </c>
       <c r="T78">
-        <v>2.867355693767022</v>
+        <v>2.992023332626458</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07235203373433539</v>
+        <v>0.07141239693259079</v>
       </c>
       <c r="W78">
-        <v>0.2187393904454437</v>
+        <v>0.2189609568032951</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3808001775491336</v>
+        <v>0.3758547206978463</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2144392036880123</v>
+        <v>0.2163392036880123</v>
       </c>
       <c r="C79">
-        <v>-44.8802830526654</v>
+        <v>-46.22401308437651</v>
       </c>
       <c r="D79">
-        <v>27.54371694733459</v>
+        <v>27.26198691562349</v>
       </c>
       <c r="E79">
-        <v>57.67399999999999</v>
+        <v>58.736</v>
       </c>
       <c r="F79">
-        <v>81.77399999999999</v>
+        <v>82.836</v>
       </c>
       <c r="G79">
         <v>9.35</v>
@@ -7765,37 +7765,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M79">
-        <v>19.2823092</v>
+        <v>19.5327288</v>
       </c>
       <c r="N79">
-        <v>-12.03496226122449</v>
+        <v>-12.28538186122449</v>
       </c>
       <c r="O79">
-        <v>-2.286642829632652</v>
+        <v>-2.334222553632653</v>
       </c>
       <c r="P79">
-        <v>-9.748319431591833</v>
+        <v>-9.951159307591837</v>
       </c>
       <c r="Q79">
-        <v>-3.628319431591833</v>
+        <v>-3.831159307591837</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1993011606498916</v>
+        <v>0.2062784861339776</v>
       </c>
       <c r="T79">
-        <v>2.992023332626458</v>
+        <v>3.128024393200388</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07141239693259079</v>
+        <v>0.07049685338217294</v>
       </c>
       <c r="W79">
-        <v>0.2189609568032951</v>
+        <v>0.2191768419724836</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3758547206978463</v>
+        <v>0.3710360704324892</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2163392036880123</v>
+        <v>0.2182392036880123</v>
       </c>
       <c r="C80">
-        <v>-46.22401308437651</v>
+        <v>-47.56203813597873</v>
       </c>
       <c r="D80">
-        <v>27.26198691562349</v>
+        <v>26.98596186402127</v>
       </c>
       <c r="E80">
-        <v>58.736</v>
+        <v>59.79799999999999</v>
       </c>
       <c r="F80">
-        <v>82.836</v>
+        <v>83.898</v>
       </c>
       <c r="G80">
         <v>9.35</v>
@@ -7847,37 +7847,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M80">
-        <v>19.5327288</v>
+        <v>19.7831484</v>
       </c>
       <c r="N80">
-        <v>-12.28538186122449</v>
+        <v>-12.53580146122449</v>
       </c>
       <c r="O80">
-        <v>-2.334222553632653</v>
+        <v>-2.381802277632652</v>
       </c>
       <c r="P80">
-        <v>-9.951159307591837</v>
+        <v>-10.15399918359184</v>
       </c>
       <c r="Q80">
-        <v>-3.831159307591837</v>
+        <v>-4.033999183591836</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2062784861339776</v>
+        <v>0.2139203188070241</v>
       </c>
       <c r="T80">
-        <v>3.128024393200388</v>
+        <v>3.276977935733739</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07049685338217294</v>
+        <v>0.06960448814948722</v>
       </c>
       <c r="W80">
-        <v>0.2191768419724836</v>
+        <v>0.2193872616943509</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3710360704324892</v>
+        <v>0.3663394113130907</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2182392036880123</v>
+        <v>0.2201392036880123</v>
       </c>
       <c r="C81">
-        <v>-47.56203813597873</v>
+        <v>-48.89452975770208</v>
       </c>
       <c r="D81">
-        <v>26.98596186402127</v>
+        <v>26.71547024229791</v>
       </c>
       <c r="E81">
-        <v>59.79799999999999</v>
+        <v>60.85999999999999</v>
       </c>
       <c r="F81">
-        <v>83.898</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="G81">
         <v>9.35</v>
@@ -7929,37 +7929,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M81">
-        <v>19.7831484</v>
+        <v>20.033568</v>
       </c>
       <c r="N81">
-        <v>-12.53580146122449</v>
+        <v>-12.78622106122449</v>
       </c>
       <c r="O81">
-        <v>-2.381802277632652</v>
+        <v>-2.429382001632653</v>
       </c>
       <c r="P81">
-        <v>-10.15399918359184</v>
+        <v>-10.35683905959183</v>
       </c>
       <c r="Q81">
-        <v>-4.033999183591836</v>
+        <v>-4.236839059591834</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2139203188070241</v>
+        <v>0.2223263347473754</v>
       </c>
       <c r="T81">
-        <v>3.276977935733739</v>
+        <v>3.440826832520427</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06960448814948722</v>
+        <v>0.06873443204761863</v>
       </c>
       <c r="W81">
-        <v>0.2193872616943509</v>
+        <v>0.2195924209231715</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3663394113130907</v>
+        <v>0.361760168671677</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2201392036880123</v>
+        <v>0.2220392036880123</v>
       </c>
       <c r="C82">
-        <v>-48.89452975770208</v>
+        <v>-50.22165268995447</v>
       </c>
       <c r="D82">
-        <v>26.71547024229791</v>
+        <v>26.45034731004553</v>
       </c>
       <c r="E82">
-        <v>60.85999999999999</v>
+        <v>61.92199999999999</v>
       </c>
       <c r="F82">
-        <v>84.95999999999999</v>
+        <v>86.02199999999999</v>
       </c>
       <c r="G82">
         <v>9.35</v>
@@ -8011,37 +8011,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M82">
-        <v>20.033568</v>
+        <v>20.2839876</v>
       </c>
       <c r="N82">
-        <v>-12.78622106122449</v>
+        <v>-13.03664066122449</v>
       </c>
       <c r="O82">
-        <v>-2.429382001632653</v>
+        <v>-2.476961725632653</v>
       </c>
       <c r="P82">
-        <v>-10.35683905959183</v>
+        <v>-10.55967893559184</v>
       </c>
       <c r="Q82">
-        <v>-4.236839059591834</v>
+        <v>-4.439678935591837</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2223263347473754</v>
+        <v>0.2316171944709215</v>
       </c>
       <c r="T82">
-        <v>3.440826832520427</v>
+        <v>3.621922981600449</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06873443204761863</v>
+        <v>0.06788585881246284</v>
       </c>
       <c r="W82">
-        <v>0.2195924209231715</v>
+        <v>0.2197925144920213</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.361760168671677</v>
+        <v>0.3572939937498044</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2220392036880123</v>
+        <v>0.2239392036880123</v>
       </c>
       <c r="C83">
-        <v>-50.22165268995447</v>
+        <v>-51.54356519790289</v>
       </c>
       <c r="D83">
-        <v>26.45034731004553</v>
+        <v>26.19043480209711</v>
       </c>
       <c r="E83">
-        <v>61.92199999999999</v>
+        <v>62.984</v>
       </c>
       <c r="F83">
-        <v>86.02199999999999</v>
+        <v>87.084</v>
       </c>
       <c r="G83">
         <v>9.35</v>
@@ -8093,37 +8093,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M83">
-        <v>20.2839876</v>
+        <v>20.5344072</v>
       </c>
       <c r="N83">
-        <v>-13.03664066122449</v>
+        <v>-13.28706026122449</v>
       </c>
       <c r="O83">
-        <v>-2.476961725632653</v>
+        <v>-2.524541449632653</v>
       </c>
       <c r="P83">
-        <v>-10.55967893559184</v>
+        <v>-10.76251881159184</v>
       </c>
       <c r="Q83">
-        <v>-4.439678935591837</v>
+        <v>-4.642518811591835</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2316171944709215</v>
+        <v>0.2419403719415283</v>
       </c>
       <c r="T83">
-        <v>3.621922981600449</v>
+        <v>3.823140925022697</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06788585881246284</v>
+        <v>0.06705798248548157</v>
       </c>
       <c r="W83">
-        <v>0.2197925144920213</v>
+        <v>0.2199877277299234</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3572939937498044</v>
+        <v>0.3529367499235874</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2239392036880123</v>
+        <v>0.2258392036880123</v>
       </c>
       <c r="C84">
-        <v>-51.54356519790289</v>
+        <v>-52.86041938652021</v>
       </c>
       <c r="D84">
-        <v>26.19043480209711</v>
+        <v>25.93558061347979</v>
       </c>
       <c r="E84">
-        <v>62.984</v>
+        <v>64.04599999999999</v>
       </c>
       <c r="F84">
-        <v>87.084</v>
+        <v>88.146</v>
       </c>
       <c r="G84">
         <v>9.35</v>
@@ -8175,37 +8175,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M84">
-        <v>20.5344072</v>
+        <v>20.7848268</v>
       </c>
       <c r="N84">
-        <v>-13.28706026122449</v>
+        <v>-13.53747986122449</v>
       </c>
       <c r="O84">
-        <v>-2.524541449632653</v>
+        <v>-2.572121173632653</v>
       </c>
       <c r="P84">
-        <v>-10.76251881159184</v>
+        <v>-10.96535868759184</v>
       </c>
       <c r="Q84">
-        <v>-4.642518811591835</v>
+        <v>-4.845358687591838</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2419403719415283</v>
+        <v>0.2534780408792652</v>
       </c>
       <c r="T84">
-        <v>3.823140925022697</v>
+        <v>4.048031567671091</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06705798248548157</v>
+        <v>0.0662500549856565</v>
       </c>
       <c r="W84">
-        <v>0.2199877277299234</v>
+        <v>0.2201782370343822</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3529367499235874</v>
+        <v>0.3486844999245079</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2258392036880123</v>
+        <v>0.2277392036880123</v>
       </c>
       <c r="C85">
-        <v>-52.86041938652021</v>
+        <v>-54.1723614974152</v>
       </c>
       <c r="D85">
-        <v>25.93558061347979</v>
+        <v>25.6856385025848</v>
       </c>
       <c r="E85">
-        <v>64.04599999999999</v>
+        <v>65.108</v>
       </c>
       <c r="F85">
-        <v>88.146</v>
+        <v>89.208</v>
       </c>
       <c r="G85">
         <v>9.35</v>
@@ -8257,37 +8257,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M85">
-        <v>20.7848268</v>
+        <v>21.0352464</v>
       </c>
       <c r="N85">
-        <v>-13.53747986122449</v>
+        <v>-13.78789946122449</v>
       </c>
       <c r="O85">
-        <v>-2.572121173632653</v>
+        <v>-2.619700897632653</v>
       </c>
       <c r="P85">
-        <v>-10.96535868759184</v>
+        <v>-11.16819856359184</v>
       </c>
       <c r="Q85">
-        <v>-4.845358687591838</v>
+        <v>-5.048198563591836</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2534780408792652</v>
+        <v>0.2664579184342193</v>
       </c>
       <c r="T85">
-        <v>4.048031567671091</v>
+        <v>4.301033540650534</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0662500549856565</v>
+        <v>0.06546136385487487</v>
       </c>
       <c r="W85">
-        <v>0.2201782370343822</v>
+        <v>0.2203642104030205</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3486844999245079</v>
+        <v>0.3445334939730257</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2277392036880123</v>
+        <v>0.2296392036880123</v>
       </c>
       <c r="C86">
-        <v>-54.17236149741518</v>
+        <v>-55.47953218866304</v>
       </c>
       <c r="D86">
-        <v>25.6856385025848</v>
+        <v>25.44046781133694</v>
       </c>
       <c r="E86">
-        <v>65.10799999999998</v>
+        <v>66.16999999999999</v>
       </c>
       <c r="F86">
-        <v>89.20799999999998</v>
+        <v>90.26999999999998</v>
       </c>
       <c r="G86">
         <v>9.35</v>
@@ -8339,37 +8339,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M86">
-        <v>21.0352464</v>
+        <v>21.285666</v>
       </c>
       <c r="N86">
-        <v>-13.78789946122449</v>
+        <v>-14.03831906122448</v>
       </c>
       <c r="O86">
-        <v>-2.619700897632653</v>
+        <v>-2.667280621632652</v>
       </c>
       <c r="P86">
-        <v>-11.16819856359183</v>
+        <v>-11.37103843959183</v>
       </c>
       <c r="Q86">
-        <v>-5.048198563591835</v>
+        <v>-5.251038439591832</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2664579184342191</v>
+        <v>0.2811684463298338</v>
       </c>
       <c r="T86">
-        <v>4.301033540650532</v>
+        <v>4.587769110027234</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06546136385487487</v>
+        <v>0.0646912301624646</v>
       </c>
       <c r="W86">
-        <v>0.2203642104030205</v>
+        <v>0.2205458079276909</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3445334939730258</v>
+        <v>0.3404801587498137</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2296392036880123</v>
+        <v>0.2315392036880123</v>
       </c>
       <c r="C87">
-        <v>-55.47953218866304</v>
+        <v>-56.78206679876146</v>
       </c>
       <c r="D87">
-        <v>25.44046781133694</v>
+        <v>25.19993320123853</v>
       </c>
       <c r="E87">
-        <v>66.16999999999999</v>
+        <v>67.232</v>
       </c>
       <c r="F87">
-        <v>90.26999999999998</v>
+        <v>91.33199999999999</v>
       </c>
       <c r="G87">
         <v>9.35</v>
@@ -8421,37 +8421,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M87">
-        <v>21.285666</v>
+        <v>21.5360856</v>
       </c>
       <c r="N87">
-        <v>-14.03831906122448</v>
+        <v>-14.28873866122449</v>
       </c>
       <c r="O87">
-        <v>-2.667280621632652</v>
+        <v>-2.714860345632653</v>
       </c>
       <c r="P87">
-        <v>-11.37103843959183</v>
+        <v>-11.57387831559184</v>
       </c>
       <c r="Q87">
-        <v>-5.251038439591832</v>
+        <v>-5.453878315591836</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2811684463298338</v>
+        <v>0.2979804782105362</v>
       </c>
       <c r="T87">
-        <v>4.587769110027234</v>
+        <v>4.915466903600608</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0646912301624646</v>
+        <v>0.0639390065559243</v>
       </c>
       <c r="W87">
-        <v>0.2205458079276909</v>
+        <v>0.2207231822541131</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3404801587498137</v>
+        <v>0.3365210871364437</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2315392036880123</v>
+        <v>0.2334392036880123</v>
       </c>
       <c r="C88">
-        <v>-56.78206679876146</v>
+        <v>-58.08009559575291</v>
       </c>
       <c r="D88">
-        <v>25.19993320123853</v>
+        <v>24.96390440424708</v>
       </c>
       <c r="E88">
-        <v>67.232</v>
+        <v>68.29399999999998</v>
       </c>
       <c r="F88">
-        <v>91.33199999999999</v>
+        <v>92.39399999999999</v>
       </c>
       <c r="G88">
         <v>9.35</v>
@@ -8503,37 +8503,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M88">
-        <v>21.5360856</v>
+        <v>21.7865052</v>
       </c>
       <c r="N88">
-        <v>-14.28873866122449</v>
+        <v>-14.53915826122449</v>
       </c>
       <c r="O88">
-        <v>-2.714860345632653</v>
+        <v>-2.762440069632653</v>
       </c>
       <c r="P88">
-        <v>-11.57387831559184</v>
+        <v>-11.77671819159184</v>
       </c>
       <c r="Q88">
-        <v>-5.453878315591836</v>
+        <v>-5.656718191591836</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2979804782105362</v>
+        <v>0.3173789765344236</v>
       </c>
       <c r="T88">
-        <v>4.915466903600608</v>
+        <v>5.293579742339117</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0639390065559243</v>
+        <v>0.0632040754460861</v>
       </c>
       <c r="W88">
-        <v>0.2207231822541131</v>
+        <v>0.2208964790098129</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3365210871364437</v>
+        <v>0.332653028663611</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2334392036880123</v>
+        <v>0.2353392036880123</v>
       </c>
       <c r="C89">
-        <v>-58.08009559575291</v>
+        <v>-59.37374401247698</v>
       </c>
       <c r="D89">
-        <v>24.96390440424708</v>
+        <v>24.73225598752301</v>
       </c>
       <c r="E89">
-        <v>68.29399999999998</v>
+        <v>69.35599999999999</v>
       </c>
       <c r="F89">
-        <v>92.39399999999999</v>
+        <v>93.45599999999999</v>
       </c>
       <c r="G89">
         <v>9.35</v>
@@ -8585,37 +8585,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M89">
-        <v>21.7865052</v>
+        <v>22.0369248</v>
       </c>
       <c r="N89">
-        <v>-14.53915826122449</v>
+        <v>-14.78957786122449</v>
       </c>
       <c r="O89">
-        <v>-2.762440069632653</v>
+        <v>-2.810019793632653</v>
       </c>
       <c r="P89">
-        <v>-11.77671819159184</v>
+        <v>-11.97955806759184</v>
       </c>
       <c r="Q89">
-        <v>-5.656718191591836</v>
+        <v>-5.859558067591835</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3173789765344236</v>
+        <v>0.3400105579122923</v>
       </c>
       <c r="T89">
-        <v>5.293579742339117</v>
+        <v>5.734711387534044</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0632040754460861</v>
+        <v>0.06248584731601693</v>
       </c>
       <c r="W89">
-        <v>0.2208964790098129</v>
+        <v>0.2210658372028832</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.332653028663611</v>
+        <v>0.3288728806106155</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2353392036880123</v>
+        <v>0.2372392036880123</v>
       </c>
       <c r="C90">
-        <v>-59.37374401247698</v>
+        <v>-60.66313286884515</v>
       </c>
       <c r="D90">
-        <v>24.73225598752301</v>
+        <v>24.50486713115484</v>
       </c>
       <c r="E90">
-        <v>69.35599999999999</v>
+        <v>70.41799999999998</v>
       </c>
       <c r="F90">
-        <v>93.45599999999999</v>
+        <v>94.51799999999999</v>
       </c>
       <c r="G90">
         <v>9.35</v>
@@ -8667,37 +8667,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M90">
-        <v>22.0369248</v>
+        <v>22.2873444</v>
       </c>
       <c r="N90">
-        <v>-14.78957786122449</v>
+        <v>-15.03999746122449</v>
       </c>
       <c r="O90">
-        <v>-2.810019793632653</v>
+        <v>-2.857599517632653</v>
       </c>
       <c r="P90">
-        <v>-11.97955806759184</v>
+        <v>-12.18239794359183</v>
       </c>
       <c r="Q90">
-        <v>-5.859558067591835</v>
+        <v>-6.062397943591834</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3400105579122923</v>
+        <v>0.3667569722679552</v>
       </c>
       <c r="T90">
-        <v>5.734711387534044</v>
+        <v>6.256048786400775</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06248584731601693</v>
+        <v>0.06178375914392686</v>
       </c>
       <c r="W90">
-        <v>0.2210658372028832</v>
+        <v>0.221231389593862</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3288728806106155</v>
+        <v>0.3251776797048782</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2372392036880123</v>
+        <v>0.2391392036880123</v>
       </c>
       <c r="C91">
-        <v>-60.66313286884515</v>
+        <v>-61.94837858196558</v>
       </c>
       <c r="D91">
-        <v>24.50486713115484</v>
+        <v>24.28162141803441</v>
       </c>
       <c r="E91">
-        <v>70.41799999999998</v>
+        <v>71.47999999999999</v>
       </c>
       <c r="F91">
-        <v>94.51799999999999</v>
+        <v>95.58</v>
       </c>
       <c r="G91">
         <v>9.35</v>
@@ -8749,37 +8749,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M91">
-        <v>22.2873444</v>
+        <v>22.537764</v>
       </c>
       <c r="N91">
-        <v>-15.03999746122449</v>
+        <v>-15.29041706122449</v>
       </c>
       <c r="O91">
-        <v>-2.857599517632653</v>
+        <v>-2.905179241632653</v>
       </c>
       <c r="P91">
-        <v>-12.18239794359183</v>
+        <v>-12.38523781959184</v>
       </c>
       <c r="Q91">
-        <v>-6.062397943591834</v>
+        <v>-6.265237819591836</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3667569722679552</v>
+        <v>0.3988526694947508</v>
       </c>
       <c r="T91">
-        <v>6.256048786400775</v>
+        <v>6.881653665040854</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06178375914392686</v>
+        <v>0.06109727293121656</v>
       </c>
       <c r="W91">
-        <v>0.221231389593862</v>
+        <v>0.2213932630428191</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3251776797048782</v>
+        <v>0.321564594374824</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2391392036880123</v>
+        <v>0.2410392036880123</v>
       </c>
       <c r="C92">
-        <v>-61.94837858196558</v>
+        <v>-63.22959336488601</v>
       </c>
       <c r="D92">
-        <v>24.28162141803441</v>
+        <v>24.06240663511399</v>
       </c>
       <c r="E92">
-        <v>71.47999999999999</v>
+        <v>72.542</v>
       </c>
       <c r="F92">
-        <v>95.58</v>
+        <v>96.642</v>
       </c>
       <c r="G92">
         <v>9.35</v>
@@ -8831,37 +8831,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M92">
-        <v>22.537764</v>
+        <v>22.7881836</v>
       </c>
       <c r="N92">
-        <v>-15.29041706122449</v>
+        <v>-15.54083666122449</v>
       </c>
       <c r="O92">
-        <v>-2.905179241632653</v>
+        <v>-2.952758965632653</v>
       </c>
       <c r="P92">
-        <v>-12.38523781959184</v>
+        <v>-12.58807769559183</v>
       </c>
       <c r="Q92">
-        <v>-6.265237819591836</v>
+        <v>-6.468077695591835</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3988526694947508</v>
+        <v>0.4380807438830564</v>
       </c>
       <c r="T92">
-        <v>6.881653665040854</v>
+        <v>7.646281850045392</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06109727293121656</v>
+        <v>0.06042587432757681</v>
       </c>
       <c r="W92">
-        <v>0.2213932630428191</v>
+        <v>0.2215515788335574</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.321564594374824</v>
+        <v>0.3180309175135622</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2410392036880123</v>
+        <v>0.2429392036880123</v>
       </c>
       <c r="C93">
-        <v>-63.22959336488601</v>
+        <v>-64.50688541466731</v>
       </c>
       <c r="D93">
-        <v>24.06240663511399</v>
+        <v>23.84711458533269</v>
       </c>
       <c r="E93">
-        <v>72.542</v>
+        <v>73.60399999999998</v>
       </c>
       <c r="F93">
-        <v>96.642</v>
+        <v>97.70399999999999</v>
       </c>
       <c r="G93">
         <v>9.35</v>
@@ -8913,37 +8913,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M93">
-        <v>22.7881836</v>
+        <v>23.0386032</v>
       </c>
       <c r="N93">
-        <v>-15.54083666122449</v>
+        <v>-15.79125626122449</v>
       </c>
       <c r="O93">
-        <v>-2.952758965632653</v>
+        <v>-3.000338689632653</v>
       </c>
       <c r="P93">
-        <v>-12.58807769559183</v>
+        <v>-12.79091757159184</v>
       </c>
       <c r="Q93">
-        <v>-6.468077695591835</v>
+        <v>-6.670917571591837</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4380807438830564</v>
+        <v>0.4871158368684387</v>
       </c>
       <c r="T93">
-        <v>7.646281850045392</v>
+        <v>8.602067081301071</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06042587432757681</v>
+        <v>0.05976907134575532</v>
       </c>
       <c r="W93">
-        <v>0.2215515788335574</v>
+        <v>0.2217064529766709</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3180309175135622</v>
+        <v>0.3145740597145017</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2429392036880123</v>
+        <v>0.2448392036880123</v>
       </c>
       <c r="C94">
-        <v>-64.50688541466731</v>
+        <v>-65.78035909045025</v>
       </c>
       <c r="D94">
-        <v>23.84711458533269</v>
+        <v>23.63564090954974</v>
       </c>
       <c r="E94">
-        <v>73.60399999999998</v>
+        <v>74.666</v>
       </c>
       <c r="F94">
-        <v>97.70399999999999</v>
+        <v>98.76599999999999</v>
       </c>
       <c r="G94">
         <v>9.35</v>
@@ -8995,37 +8995,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M94">
-        <v>23.0386032</v>
+        <v>23.2890228</v>
       </c>
       <c r="N94">
-        <v>-15.79125626122449</v>
+        <v>-16.04167586122449</v>
       </c>
       <c r="O94">
-        <v>-3.000338689632653</v>
+        <v>-3.047918413632653</v>
       </c>
       <c r="P94">
-        <v>-12.79091757159184</v>
+        <v>-12.99375744759183</v>
       </c>
       <c r="Q94">
-        <v>-6.670917571591837</v>
+        <v>-6.873757447591834</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4871158368684387</v>
+        <v>0.5501609564210727</v>
       </c>
       <c r="T94">
-        <v>8.602067081301071</v>
+        <v>9.830933807201223</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05976907134575532</v>
+        <v>0.05912639315924183</v>
       </c>
       <c r="W94">
-        <v>0.2217064529766709</v>
+        <v>0.2218579964930508</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3145740597145017</v>
+        <v>0.3111915429433781</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2448392036880123</v>
+        <v>0.2467392036880123</v>
       </c>
       <c r="C95">
-        <v>-65.78035909045025</v>
+        <v>-67.05011508213106</v>
       </c>
       <c r="D95">
-        <v>23.63564090954974</v>
+        <v>23.42788491786893</v>
       </c>
       <c r="E95">
-        <v>74.666</v>
+        <v>75.72799999999998</v>
       </c>
       <c r="F95">
-        <v>98.76599999999999</v>
+        <v>99.82799999999999</v>
       </c>
       <c r="G95">
         <v>9.35</v>
@@ -9077,37 +9077,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M95">
-        <v>23.2890228</v>
+        <v>23.5394424</v>
       </c>
       <c r="N95">
-        <v>-16.04167586122449</v>
+        <v>-16.29209546122449</v>
       </c>
       <c r="O95">
-        <v>-3.047918413632653</v>
+        <v>-3.095498137632653</v>
       </c>
       <c r="P95">
-        <v>-12.99375744759183</v>
+        <v>-13.19659732359183</v>
       </c>
       <c r="Q95">
-        <v>-6.873757447591834</v>
+        <v>-7.076597323591835</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5501609564210727</v>
+        <v>0.6342211158245851</v>
       </c>
       <c r="T95">
-        <v>9.830933807201223</v>
+        <v>11.4694227750681</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05912639315924183</v>
+        <v>0.0584973889766967</v>
       </c>
       <c r="W95">
-        <v>0.2218579964930508</v>
+        <v>0.2220063156792949</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3111915429433781</v>
+        <v>0.3078809946141932</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2467392036880123</v>
+        <v>0.2486392036880123</v>
       </c>
       <c r="C96">
-        <v>-67.05011508213106</v>
+        <v>-68.31625057021853</v>
       </c>
       <c r="D96">
-        <v>23.42788491786893</v>
+        <v>23.22374942978147</v>
       </c>
       <c r="E96">
-        <v>75.72799999999998</v>
+        <v>76.78999999999999</v>
       </c>
       <c r="F96">
-        <v>99.82799999999999</v>
+        <v>100.89</v>
       </c>
       <c r="G96">
         <v>9.35</v>
@@ -9159,37 +9159,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M96">
-        <v>23.5394424</v>
+        <v>23.789862</v>
       </c>
       <c r="N96">
-        <v>-16.29209546122449</v>
+        <v>-16.54251506122449</v>
       </c>
       <c r="O96">
-        <v>-3.095498137632653</v>
+        <v>-3.143077861632653</v>
       </c>
       <c r="P96">
-        <v>-13.19659732359183</v>
+        <v>-13.39943719959184</v>
       </c>
       <c r="Q96">
-        <v>-7.076597323591835</v>
+        <v>-7.279437199591835</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6342211158245851</v>
+        <v>0.7519053389895022</v>
       </c>
       <c r="T96">
-        <v>11.4694227750681</v>
+        <v>13.76330733008172</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0584973889766967</v>
+        <v>0.05788162698746832</v>
       </c>
       <c r="W96">
-        <v>0.2220063156792949</v>
+        <v>0.222151512356355</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3078809946141932</v>
+        <v>0.304640142039307</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2486392036880123</v>
+        <v>0.2505392036880123</v>
       </c>
       <c r="C97">
-        <v>-68.31625057021853</v>
+        <v>-69.57885937740602</v>
       </c>
       <c r="D97">
-        <v>23.22374942978147</v>
+        <v>23.02314062259397</v>
       </c>
       <c r="E97">
-        <v>76.78999999999999</v>
+        <v>77.852</v>
       </c>
       <c r="F97">
-        <v>100.89</v>
+        <v>101.952</v>
       </c>
       <c r="G97">
         <v>9.35</v>
@@ -9241,37 +9241,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M97">
-        <v>23.789862</v>
+        <v>24.0402816</v>
       </c>
       <c r="N97">
-        <v>-16.54251506122449</v>
+        <v>-16.79293466122449</v>
       </c>
       <c r="O97">
-        <v>-3.143077861632653</v>
+        <v>-3.190657585632653</v>
       </c>
       <c r="P97">
-        <v>-13.39943719959184</v>
+        <v>-13.60227707559184</v>
       </c>
       <c r="Q97">
-        <v>-7.279437199591835</v>
+        <v>-7.482277075591836</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7519053389895022</v>
+        <v>0.9284316737368784</v>
       </c>
       <c r="T97">
-        <v>13.76330733008172</v>
+        <v>17.20413416260216</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05788162698746832</v>
+        <v>0.05727869337301552</v>
       </c>
       <c r="W97">
-        <v>0.222151512356355</v>
+        <v>0.2222936841026429</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.304640142039307</v>
+        <v>0.3014668072263975</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2505392036880123</v>
+        <v>0.2524392036880123</v>
       </c>
       <c r="C98">
-        <v>-69.57885937740602</v>
+        <v>-70.83803211235502</v>
       </c>
       <c r="D98">
-        <v>23.02314062259397</v>
+        <v>22.82596788764497</v>
       </c>
       <c r="E98">
-        <v>77.85199999999998</v>
+        <v>78.91399999999999</v>
       </c>
       <c r="F98">
-        <v>101.952</v>
+        <v>103.014</v>
       </c>
       <c r="G98">
         <v>9.35</v>
@@ -9323,37 +9323,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M98">
-        <v>24.0402816</v>
+        <v>24.2907012</v>
       </c>
       <c r="N98">
-        <v>-16.79293466122449</v>
+        <v>-17.04335426122449</v>
       </c>
       <c r="O98">
-        <v>-3.190657585632652</v>
+        <v>-3.238237309632653</v>
       </c>
       <c r="P98">
-        <v>-13.60227707559183</v>
+        <v>-13.80511695159183</v>
       </c>
       <c r="Q98">
-        <v>-7.482277075591832</v>
+        <v>-7.685116951591834</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.928431673736876</v>
+        <v>1.222642231649168</v>
       </c>
       <c r="T98">
-        <v>17.20413416260212</v>
+        <v>22.93884555013615</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05727869337301553</v>
+        <v>0.05668819137947929</v>
       </c>
       <c r="W98">
-        <v>0.2222936841026429</v>
+        <v>0.2224329244727188</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3014668072263975</v>
+        <v>0.2983589019972595</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2524392036880123</v>
+        <v>0.2543392036880123</v>
       </c>
       <c r="C99">
-        <v>-70.83803211235502</v>
+        <v>-72.09385630615313</v>
       </c>
       <c r="D99">
-        <v>22.82596788764497</v>
+        <v>22.63214369384686</v>
       </c>
       <c r="E99">
-        <v>78.91399999999999</v>
+        <v>79.976</v>
       </c>
       <c r="F99">
-        <v>103.014</v>
+        <v>104.076</v>
       </c>
       <c r="G99">
         <v>9.35</v>
@@ -9405,37 +9405,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M99">
-        <v>24.2907012</v>
+        <v>24.5411208</v>
       </c>
       <c r="N99">
-        <v>-17.04335426122449</v>
+        <v>-17.29377386122449</v>
       </c>
       <c r="O99">
-        <v>-3.238237309632653</v>
+        <v>-3.285817033632652</v>
       </c>
       <c r="P99">
-        <v>-13.80511695159183</v>
+        <v>-14.00795682759184</v>
       </c>
       <c r="Q99">
-        <v>-7.685116951591834</v>
+        <v>-7.887956827591835</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.222642231649168</v>
+        <v>1.811063347473752</v>
       </c>
       <c r="T99">
-        <v>22.93884555013615</v>
+        <v>34.40826832520423</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05668819137947929</v>
+        <v>0.05610974044703562</v>
       </c>
       <c r="W99">
-        <v>0.2224329244727188</v>
+        <v>0.222569323202589</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2983589019972595</v>
+        <v>0.2953144234054507</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2543392036880123</v>
+        <v>0.2562392036880123</v>
       </c>
       <c r="C100">
-        <v>-72.09385630615313</v>
+        <v>-73.34641654187824</v>
       </c>
       <c r="D100">
-        <v>22.63214369384686</v>
+        <v>22.44158345812175</v>
       </c>
       <c r="E100">
-        <v>79.976</v>
+        <v>81.03799999999998</v>
       </c>
       <c r="F100">
-        <v>104.076</v>
+        <v>105.138</v>
       </c>
       <c r="G100">
         <v>9.35</v>
@@ -9487,37 +9487,37 @@
         <v>7.24734693877551</v>
       </c>
       <c r="M100">
-        <v>24.5411208</v>
+        <v>24.7915404</v>
       </c>
       <c r="N100">
-        <v>-17.29377386122449</v>
+        <v>-17.54419346122449</v>
       </c>
       <c r="O100">
-        <v>-3.285817033632652</v>
+        <v>-3.333396757632653</v>
       </c>
       <c r="P100">
-        <v>-14.00795682759184</v>
+        <v>-14.21079670359184</v>
       </c>
       <c r="Q100">
-        <v>-7.887956827591835</v>
+        <v>-8.090796703591835</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.811063347473752</v>
+        <v>3.576326694947504</v>
       </c>
       <c r="T100">
-        <v>34.40826832520423</v>
+        <v>68.81653665040847</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05610974044703562</v>
+        <v>0.05554297539201505</v>
       </c>
       <c r="W100">
-        <v>0.222569323202589</v>
+        <v>0.2227029664025629</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2953144234054507</v>
+        <v>0.2923314494316582</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2562392036880123</v>
-      </c>
-      <c r="C101">
-        <v>-73.34641654187824</v>
-      </c>
-      <c r="D101">
-        <v>22.44158345812175</v>
-      </c>
-      <c r="E101">
-        <v>81.03799999999998</v>
-      </c>
-      <c r="F101">
-        <v>105.138</v>
-      </c>
-      <c r="G101">
-        <v>9.35</v>
-      </c>
-      <c r="H101">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>13.36734693877551</v>
-      </c>
-      <c r="K101">
-        <v>6.12</v>
-      </c>
-      <c r="L101">
-        <v>7.24734693877551</v>
-      </c>
-      <c r="M101">
-        <v>24.7915404</v>
-      </c>
-      <c r="N101">
-        <v>-17.54419346122449</v>
-      </c>
-      <c r="O101">
-        <v>-3.333396757632653</v>
-      </c>
-      <c r="P101">
-        <v>-14.21079670359184</v>
-      </c>
-      <c r="Q101">
-        <v>-8.090796703591835</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.576326694947504</v>
-      </c>
-      <c r="T101">
-        <v>68.81653665040847</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05554297539201505</v>
-      </c>
-      <c r="W101">
-        <v>0.2227029664025629</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2923314494316582</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
